--- a/ozone/multistate/train_ozone_VTZP_MS_3_70_30_energies.xlsx
+++ b/ozone/multistate/train_ozone_VTZP_MS_3_70_30_energies.xlsx
@@ -485,7 +485,7 @@
         <v>-0.5722291819875045</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.5721298456192017</v>
+        <v>-0.5715935230255127</v>
       </c>
       <c r="F2" t="n">
         <v>-225.159891</v>
@@ -494,7 +494,7 @@
         <v>-224.5876625</v>
       </c>
       <c r="H2" t="n">
-        <v>-225.1597923456192</v>
+        <v>-225.1592560230255</v>
       </c>
     </row>
     <row r="3">
@@ -517,7 +517,7 @@
         <v>-0.5715404485286815</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.5688276886940002</v>
+        <v>-0.5688554644584656</v>
       </c>
       <c r="F3" t="n">
         <v>-225.16985899</v>
@@ -526,7 +526,7 @@
         <v>-224.59832086</v>
       </c>
       <c r="H3" t="n">
-        <v>-225.167148548694</v>
+        <v>-225.1671763244585</v>
       </c>
     </row>
     <row r="4">
@@ -549,7 +549,7 @@
         <v>-0.5710394868419331</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.5686130523681641</v>
+        <v>-0.5712248682975769</v>
       </c>
       <c r="F4" t="n">
         <v>-225.1779703</v>
@@ -558,7 +558,7 @@
         <v>-224.60693086</v>
       </c>
       <c r="H4" t="n">
-        <v>-225.1755439123682</v>
+        <v>-225.1781557282976</v>
       </c>
     </row>
     <row r="5">
@@ -581,7 +581,7 @@
         <v>-0.5757519096066617</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.582574725151062</v>
+        <v>-0.5848411917686462</v>
       </c>
       <c r="F5" t="n">
         <v>-225.12331019</v>
@@ -590,7 +590,7 @@
         <v>-224.54756031</v>
       </c>
       <c r="H5" t="n">
-        <v>-225.1301350351511</v>
+        <v>-225.1324015017686</v>
       </c>
     </row>
     <row r="6">
@@ -613,7 +613,7 @@
         <v>-0.6122157322350953</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.6145563125610352</v>
+        <v>-0.6128999590873718</v>
       </c>
       <c r="F6" t="n">
         <v>-225.15491327</v>
@@ -622,7 +622,7 @@
         <v>-224.54269476</v>
       </c>
       <c r="H6" t="n">
-        <v>-225.157251072561</v>
+        <v>-225.1555947190874</v>
       </c>
     </row>
     <row r="7">
@@ -645,7 +645,7 @@
         <v>-0.5735418751654208</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.5763770341873169</v>
+        <v>-0.575319766998291</v>
       </c>
       <c r="F7" t="n">
         <v>-225.14390949</v>
@@ -654,7 +654,7 @@
         <v>-224.57036624</v>
       </c>
       <c r="H7" t="n">
-        <v>-225.1467432741873</v>
+        <v>-225.1456860069983</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         <v>-0.5718434629383771</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.5673929452896118</v>
+        <v>-0.570286750793457</v>
       </c>
       <c r="F8" t="n">
         <v>-225.16530615</v>
@@ -686,7 +686,7 @@
         <v>-224.59346379</v>
       </c>
       <c r="H8" t="n">
-        <v>-225.1608567352896</v>
+        <v>-225.1637505407934</v>
       </c>
     </row>
     <row r="9">
@@ -709,7 +709,7 @@
         <v>-0.5703494623688888</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.5691424608230591</v>
+        <v>-0.5689279437065125</v>
       </c>
       <c r="F9" t="n">
         <v>-225.2098853</v>
@@ -718,7 +718,7 @@
         <v>-224.63953823</v>
       </c>
       <c r="H9" t="n">
-        <v>-225.2086806908231</v>
+        <v>-225.2084661737065</v>
       </c>
     </row>
     <row r="10">
@@ -741,7 +741,7 @@
         <v>-0.5729111570893592</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.5721205472946167</v>
+        <v>-0.5722969770431519</v>
       </c>
       <c r="F10" t="n">
         <v>-225.22005571</v>
@@ -750,7 +750,7 @@
         <v>-224.64714128</v>
       </c>
       <c r="H10" t="n">
-        <v>-225.2192618272946</v>
+        <v>-225.2194382570432</v>
       </c>
     </row>
     <row r="11">
@@ -773,7 +773,7 @@
         <v>-0.5740850584291357</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.5756418108940125</v>
+        <v>-0.5748420357704163</v>
       </c>
       <c r="F11" t="n">
         <v>-225.13818118</v>
@@ -782,7 +782,7 @@
         <v>-224.56409176</v>
       </c>
       <c r="H11" t="n">
-        <v>-225.139733570894</v>
+        <v>-225.1389337957704</v>
       </c>
     </row>
     <row r="12">
@@ -805,7 +805,7 @@
         <v>-0.5737860654806543</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.5758755207061768</v>
+        <v>-0.574286162853241</v>
       </c>
       <c r="F12" t="n">
         <v>-225.22228359</v>
@@ -814,7 +814,7 @@
         <v>-224.64849613</v>
       </c>
       <c r="H12" t="n">
-        <v>-225.2243716507062</v>
+        <v>-225.2227822928533</v>
       </c>
     </row>
     <row r="13">
@@ -837,7 +837,7 @@
         <v>-0.6075337210639622</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.608063817024231</v>
+        <v>-0.6085098385810852</v>
       </c>
       <c r="F13" t="n">
         <v>-225.15287941</v>
@@ -846,7 +846,7 @@
         <v>-224.54534556</v>
       </c>
       <c r="H13" t="n">
-        <v>-225.1534093770242</v>
+        <v>-225.1538553985811</v>
       </c>
     </row>
     <row r="14">
@@ -869,7 +869,7 @@
         <v>-0.5762879540237973</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.5783200860023499</v>
+        <v>-0.5763528347015381</v>
       </c>
       <c r="F14" t="n">
         <v>-225.11918185</v>
@@ -878,7 +878,7 @@
         <v>-224.54289349</v>
       </c>
       <c r="H14" t="n">
-        <v>-225.1212135760024</v>
+        <v>-225.1192463247015</v>
       </c>
     </row>
     <row r="15">
@@ -901,7 +901,7 @@
         <v>-0.5735269839594007</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.574400007724762</v>
+        <v>-0.5726367831230164</v>
       </c>
       <c r="F15" t="n">
         <v>-225.22168789</v>
@@ -910,7 +910,7 @@
         <v>-224.64816064</v>
       </c>
       <c r="H15" t="n">
-        <v>-225.2225606477247</v>
+        <v>-225.220797423123</v>
       </c>
     </row>
     <row r="16">
@@ -933,7 +933,7 @@
         <v>-0.5996908809927513</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.6009262800216675</v>
+        <v>-0.6016646027565002</v>
       </c>
       <c r="F16" t="n">
         <v>-225.14954796</v>
@@ -942,7 +942,7 @@
         <v>-224.54985758</v>
       </c>
       <c r="H16" t="n">
-        <v>-225.1507838600217</v>
+        <v>-225.1515221827565</v>
       </c>
     </row>
     <row r="17">
@@ -965,7 +965,7 @@
         <v>-0.5732668997719599</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.5750436782836914</v>
+        <v>-0.5739274621009827</v>
       </c>
       <c r="F17" t="n">
         <v>-225.22103032</v>
@@ -974,7 +974,7 @@
         <v>-224.6477647</v>
       </c>
       <c r="H17" t="n">
-        <v>-225.2228083782837</v>
+        <v>-225.221692162101</v>
       </c>
     </row>
     <row r="18">
@@ -997,7 +997,7 @@
         <v>-0.5696606225578875</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.56809401512146</v>
+        <v>-0.5689078569412231</v>
       </c>
       <c r="F18" t="n">
         <v>-225.20732691</v>
@@ -1006,7 +1006,7 @@
         <v>-224.63766328</v>
       </c>
       <c r="H18" t="n">
-        <v>-225.2057572951215</v>
+        <v>-225.2065711369412</v>
       </c>
     </row>
     <row r="19">
@@ -1029,7 +1029,7 @@
         <v>-0.6044762619047506</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.6037989854812622</v>
+        <v>-0.6042691469192505</v>
       </c>
       <c r="F19" t="n">
         <v>-225.15155721</v>
@@ -1038,7 +1038,7 @@
         <v>-224.54707928</v>
       </c>
       <c r="H19" t="n">
-        <v>-225.1508782654813</v>
+        <v>-225.1513484269192</v>
       </c>
     </row>
     <row r="20">
@@ -1061,7 +1061,7 @@
         <v>-0.6051862327254006</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.6035952568054199</v>
+        <v>-0.6036413908004761</v>
       </c>
       <c r="F20" t="n">
         <v>-225.15186078</v>
@@ -1070,7 +1070,7 @@
         <v>-224.54667446</v>
       </c>
       <c r="H20" t="n">
-        <v>-225.1502697168054</v>
+        <v>-225.1503158508005</v>
       </c>
     </row>
     <row r="21">
@@ -1093,7 +1093,7 @@
         <v>-0.6068014048398889</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.6097161769866943</v>
+        <v>-0.6076752543449402</v>
       </c>
       <c r="F21" t="n">
         <v>-225.15255914</v>
@@ -1102,7 +1102,7 @@
         <v>-224.54575855</v>
       </c>
       <c r="H21" t="n">
-        <v>-225.1554747269867</v>
+        <v>-225.1534338043449</v>
       </c>
     </row>
     <row r="22">
@@ -1125,7 +1125,7 @@
         <v>-0.5697975388104934</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.5695058107376099</v>
+        <v>-0.5728913545608521</v>
       </c>
       <c r="F22" t="n">
         <v>-225.20381303</v>
@@ -1134,7 +1134,7 @@
         <v>-224.63402045</v>
       </c>
       <c r="H22" t="n">
-        <v>-225.2035262607376</v>
+        <v>-225.2069118045609</v>
       </c>
     </row>
     <row r="23">
@@ -1157,7 +1157,7 @@
         <v>-0.6023644353471276</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.601366400718689</v>
+        <v>-0.6013655662536621</v>
       </c>
       <c r="F23" t="n">
         <v>-225.15066251</v>
@@ -1166,7 +1166,7 @@
         <v>-224.54829896</v>
       </c>
       <c r="H23" t="n">
-        <v>-225.1496653607187</v>
+        <v>-225.1496645262537</v>
       </c>
     </row>
     <row r="24">
@@ -1189,7 +1189,7 @@
         <v>-0.572057491396363</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.5676765441894531</v>
+        <v>-0.5706512928009033</v>
       </c>
       <c r="F24" t="n">
         <v>-225.1622248</v>
@@ -1198,7 +1198,7 @@
         <v>-224.59016607</v>
       </c>
       <c r="H24" t="n">
-        <v>-225.1578426141895</v>
+        <v>-225.1608173628009</v>
       </c>
     </row>
     <row r="25">
@@ -1221,7 +1221,7 @@
         <v>-0.5736957010600274</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.5758568048477173</v>
+        <v>-0.5740368366241455</v>
       </c>
       <c r="F25" t="n">
         <v>-225.14227809</v>
@@ -1230,7 +1230,7 @@
         <v>-224.56858375</v>
       </c>
       <c r="H25" t="n">
-        <v>-225.1444405548477</v>
+        <v>-225.1426205866241</v>
       </c>
     </row>
     <row r="26">
@@ -1253,7 +1253,7 @@
         <v>-0.5712130685560088</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.5674667358398438</v>
+        <v>-0.568788468837738</v>
       </c>
       <c r="F26" t="n">
         <v>-225.17505779</v>
@@ -1262,7 +1262,7 @@
         <v>-224.60384545</v>
       </c>
       <c r="H26" t="n">
-        <v>-225.1713121858398</v>
+        <v>-225.1726339188377</v>
       </c>
     </row>
     <row r="27">
@@ -1285,7 +1285,7 @@
         <v>-0.6129363580607732</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.6130408048629761</v>
+        <v>-0.6119785904884338</v>
       </c>
       <c r="F27" t="n">
         <v>-225.15520998</v>
@@ -1294,7 +1294,7 @@
         <v>-224.54227374</v>
       </c>
       <c r="H27" t="n">
-        <v>-225.155314544863</v>
+        <v>-225.1542523304884</v>
       </c>
     </row>
     <row r="28">
@@ -1317,7 +1317,7 @@
         <v>-0.5718384683188923</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.5714997053146362</v>
+        <v>-0.5725995302200317</v>
       </c>
       <c r="F28" t="n">
         <v>-225.21643284</v>
@@ -1326,7 +1326,7 @@
         <v>-224.64459315</v>
       </c>
       <c r="H28" t="n">
-        <v>-225.2160928553146</v>
+        <v>-225.21719268022</v>
       </c>
     </row>
     <row r="29">
@@ -1349,7 +1349,7 @@
         <v>-0.609050904995579</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.6079071760177612</v>
+        <v>-0.6064692735671997</v>
       </c>
       <c r="F29" t="n">
         <v>-225.15354504</v>
@@ -1358,7 +1358,7 @@
         <v>-224.54449421</v>
       </c>
       <c r="H29" t="n">
-        <v>-225.1524013860178</v>
+        <v>-225.1509634835672</v>
       </c>
     </row>
     <row r="30">
@@ -1381,7 +1381,7 @@
         <v>-0.6069803921387871</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.609249472618103</v>
+        <v>-0.6086747646331787</v>
       </c>
       <c r="F30" t="n">
         <v>-225.15263856</v>
@@ -1390,7 +1390,7 @@
         <v>-224.54565581</v>
       </c>
       <c r="H30" t="n">
-        <v>-225.1549052826181</v>
+        <v>-225.1543305746332</v>
       </c>
     </row>
     <row r="31">
@@ -1413,7 +1413,7 @@
         <v>-0.6077186382705579</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.607779860496521</v>
+        <v>-0.6080939769744873</v>
       </c>
       <c r="F31" t="n">
         <v>-225.15296075</v>
@@ -1422,7 +1422,7 @@
         <v>-224.54524121</v>
       </c>
       <c r="H31" t="n">
-        <v>-225.1530210704965</v>
+        <v>-225.1533351869745</v>
       </c>
     </row>
     <row r="32">
@@ -1445,7 +1445,7 @@
         <v>-0.6178720971909979</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.6193548440933228</v>
+        <v>-0.6163760423660278</v>
       </c>
       <c r="F32" t="n">
         <v>-225.15700403</v>
@@ -1454,7 +1454,7 @@
         <v>-224.53913558</v>
       </c>
       <c r="H32" t="n">
-        <v>-225.1584904240933</v>
+        <v>-225.155511622366</v>
       </c>
     </row>
     <row r="33">
@@ -1477,7 +1477,7 @@
         <v>-0.5711676682320826</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.5672017335891724</v>
+        <v>-0.5685903429985046</v>
       </c>
       <c r="F33" t="n">
         <v>-225.17578989</v>
@@ -1486,7 +1486,7 @@
         <v>-224.60462164</v>
       </c>
       <c r="H33" t="n">
-        <v>-225.1718233735892</v>
+        <v>-225.1732119829985</v>
       </c>
     </row>
     <row r="34">
@@ -1509,7 +1509,7 @@
         <v>-0.5726489664929151</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.5731436014175415</v>
+        <v>-0.5752630829811096</v>
       </c>
       <c r="F34" t="n">
         <v>-225.21924945</v>
@@ -1518,7 +1518,7 @@
         <v>-224.64660048</v>
       </c>
       <c r="H34" t="n">
-        <v>-225.2197440814175</v>
+        <v>-225.2218635629811</v>
       </c>
     </row>
     <row r="35">
@@ -1541,7 +1541,7 @@
         <v>-0.6117592953364577</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.6135691404342651</v>
+        <v>-0.6130550503730774</v>
       </c>
       <c r="F35" t="n">
         <v>-225.15472017</v>
@@ -1550,7 +1550,7 @@
         <v>-224.54296013</v>
       </c>
       <c r="H35" t="n">
-        <v>-225.1565292704343</v>
+        <v>-225.1560151803731</v>
       </c>
     </row>
     <row r="36">
@@ -1573,7 +1573,7 @@
         <v>-0.5717882429631447</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.5716009736061096</v>
+        <v>-0.5733848810195923</v>
       </c>
       <c r="F36" t="n">
         <v>-225.16607067</v>
@@ -1582,7 +1582,7 @@
         <v>-224.59428064</v>
       </c>
       <c r="H36" t="n">
-        <v>-225.1658816136061</v>
+        <v>-225.1676655210196</v>
       </c>
     </row>
     <row r="37">
@@ -1605,7 +1605,7 @@
         <v>-0.5719309629901309</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.5728630423545837</v>
+        <v>-0.5745717287063599</v>
       </c>
       <c r="F37" t="n">
         <v>-225.21677598</v>
@@ -1614,7 +1614,7 @@
         <v>-224.64484545</v>
       </c>
       <c r="H37" t="n">
-        <v>-225.2177084923546</v>
+        <v>-225.2194171787064</v>
       </c>
     </row>
     <row r="38">
@@ -1637,7 +1637,7 @@
         <v>-0.6062563871896278</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.6096078753471375</v>
+        <v>-0.6093505620956421</v>
       </c>
       <c r="F38" t="n">
         <v>-225.15232321</v>
@@ -1646,7 +1646,7 @@
         <v>-224.54606538</v>
       </c>
       <c r="H38" t="n">
-        <v>-225.1556732553471</v>
+        <v>-225.1554159420956</v>
       </c>
     </row>
     <row r="39">
@@ -1669,7 +1669,7 @@
         <v>-0.56958428946927</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.5694520473480225</v>
+        <v>-0.5699723958969116</v>
       </c>
       <c r="F39" t="n">
         <v>-225.2095936</v>
@@ -1678,7 +1678,7 @@
         <v>-224.64000756</v>
       </c>
       <c r="H39" t="n">
-        <v>-225.209459607348</v>
+        <v>-225.2099799558969</v>
       </c>
     </row>
     <row r="40">
@@ -1701,7 +1701,7 @@
         <v>-0.5695520769204746</v>
       </c>
       <c r="E40" t="n">
-        <v>-0.5694218277931213</v>
+        <v>-0.567686915397644</v>
       </c>
       <c r="F40" t="n">
         <v>-225.21070369</v>
@@ -1710,7 +1710,7 @@
         <v>-224.64115395</v>
       </c>
       <c r="H40" t="n">
-        <v>-225.2105757777931</v>
+        <v>-225.2088408653976</v>
       </c>
     </row>
     <row r="41">
@@ -1733,7 +1733,7 @@
         <v>-0.6082840757335015</v>
       </c>
       <c r="E41" t="n">
-        <v>-0.6081268787384033</v>
+        <v>-0.6084988117218018</v>
       </c>
       <c r="F41" t="n">
         <v>-225.15320785</v>
@@ -1742,7 +1742,7 @@
         <v>-224.54492485</v>
       </c>
       <c r="H41" t="n">
-        <v>-225.1530517287384</v>
+        <v>-225.1534236617218</v>
       </c>
     </row>
     <row r="42">
@@ -1765,7 +1765,7 @@
         <v>-0.5730917360816121</v>
       </c>
       <c r="E42" t="n">
-        <v>-0.5723505020141602</v>
+        <v>-0.5733650922775269</v>
       </c>
       <c r="F42" t="n">
         <v>-225.22055719</v>
@@ -1774,7 +1774,7 @@
         <v>-224.64746703</v>
       </c>
       <c r="H42" t="n">
-        <v>-225.2198175320142</v>
+        <v>-225.2208321222775</v>
       </c>
     </row>
     <row r="43">
@@ -1797,7 +1797,7 @@
         <v>-0.5746462919990711</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.5702954530715942</v>
+        <v>-0.5698639750480652</v>
       </c>
       <c r="F43" t="n">
         <v>-225.22383828</v>
@@ -1806,7 +1806,7 @@
         <v>-224.64919121</v>
       </c>
       <c r="H43" t="n">
-        <v>-225.2194866630716</v>
+        <v>-225.2190551850481</v>
       </c>
     </row>
     <row r="44">
@@ -1829,7 +1829,7 @@
         <v>-0.5989648740441806</v>
       </c>
       <c r="E44" t="n">
-        <v>-0.5966643095016479</v>
+        <v>-0.6004092693328857</v>
       </c>
       <c r="F44" t="n">
         <v>-225.14924704</v>
@@ -1838,7 +1838,7 @@
         <v>-224.55028253</v>
       </c>
       <c r="H44" t="n">
-        <v>-225.1469468395017</v>
+        <v>-225.1506917993329</v>
       </c>
     </row>
     <row r="45">
@@ -1861,7 +1861,7 @@
         <v>-0.5753467631900482</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.5773359537124634</v>
+        <v>-0.5802879333496094</v>
       </c>
       <c r="F45" t="n">
         <v>-225.12661997</v>
@@ -1870,7 +1870,7 @@
         <v>-224.55127455</v>
       </c>
       <c r="H45" t="n">
-        <v>-225.1286105037125</v>
+        <v>-225.1315624833496</v>
       </c>
     </row>
     <row r="46">
@@ -1893,7 +1893,7 @@
         <v>-0.5978622480348266</v>
       </c>
       <c r="E46" t="n">
-        <v>-0.6008484363555908</v>
+        <v>-0.5989652872085571</v>
       </c>
       <c r="F46" t="n">
         <v>-225.14879146</v>
@@ -1902,7 +1902,7 @@
         <v>-224.55092714</v>
       </c>
       <c r="H46" t="n">
-        <v>-225.1517755763556</v>
+        <v>-225.1498924272086</v>
       </c>
     </row>
     <row r="47">
@@ -1925,7 +1925,7 @@
         <v>-0.5730013738499149</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.5728996992111206</v>
+        <v>-0.5731385350227356</v>
       </c>
       <c r="F47" t="n">
         <v>-225.22030986</v>
@@ -1934,7 +1934,7 @@
         <v>-224.64730754</v>
       </c>
       <c r="H47" t="n">
-        <v>-225.2202072392111</v>
+        <v>-225.2204460750227</v>
       </c>
     </row>
     <row r="48">
@@ -1957,7 +1957,7 @@
         <v>-0.5694979320117856</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.5699248313903809</v>
+        <v>-0.5680090188980103</v>
       </c>
       <c r="F48" t="n">
         <v>-225.21233885</v>
@@ -1966,7 +1966,7 @@
         <v>-224.64284039</v>
       </c>
       <c r="H48" t="n">
-        <v>-225.2127652213904</v>
+        <v>-225.210849408898</v>
       </c>
     </row>
     <row r="49">
@@ -1989,7 +1989,7 @@
         <v>-0.5716373608813199</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.5706319808959961</v>
+        <v>-0.5706346035003662</v>
       </c>
       <c r="F49" t="n">
         <v>-225.16835081</v>
@@ -1998,7 +1998,7 @@
         <v>-224.59671388</v>
       </c>
       <c r="H49" t="n">
-        <v>-225.167345860896</v>
+        <v>-225.1673484835004</v>
       </c>
     </row>
     <row r="50">
@@ -2021,7 +2021,7 @@
         <v>-0.5694678538621445</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.5706207752227783</v>
+        <v>-0.5694922208786011</v>
       </c>
       <c r="F50" t="n">
         <v>-225.21340917</v>
@@ -2030,7 +2030,7 @@
         <v>-224.64394293</v>
       </c>
       <c r="H50" t="n">
-        <v>-225.2145637052228</v>
+        <v>-225.2134351508786</v>
       </c>
     </row>
     <row r="51">
@@ -2053,7 +2053,7 @@
         <v>-0.5995099742146655</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.5999170541763306</v>
+        <v>-0.5992427468299866</v>
       </c>
       <c r="F51" t="n">
         <v>-225.14947303</v>
@@ -2062,7 +2062,7 @@
         <v>-224.54996334</v>
       </c>
       <c r="H51" t="n">
-        <v>-225.1498803941763</v>
+        <v>-225.14920608683</v>
       </c>
     </row>
     <row r="52">
@@ -2085,7 +2085,7 @@
         <v>-0.5720223319340143</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.572742223739624</v>
+        <v>-0.5745524168014526</v>
       </c>
       <c r="F52" t="n">
         <v>-225.21711121</v>
@@ -2094,7 +2094,7 @@
         <v>-224.64509024</v>
       </c>
       <c r="H52" t="n">
-        <v>-225.2178324637396</v>
+        <v>-225.2196426568015</v>
       </c>
     </row>
     <row r="53">
@@ -2117,7 +2117,7 @@
         <v>-0.6137031125343466</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.6139362454414368</v>
+        <v>-0.6143544912338257</v>
       </c>
       <c r="F53" t="n">
         <v>-225.15551594</v>
@@ -2126,7 +2126,7 @@
         <v>-224.54181912</v>
       </c>
       <c r="H53" t="n">
-        <v>-225.1557553654415</v>
+        <v>-225.1561736112338</v>
       </c>
     </row>
     <row r="54">
@@ -2149,7 +2149,7 @@
         <v>-0.5703072755718729</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.5717544555664062</v>
+        <v>-0.5726728439331055</v>
       </c>
       <c r="F54" t="n">
         <v>-225.19183774</v>
@@ -2158,7 +2158,7 @@
         <v>-224.62153105</v>
       </c>
       <c r="H54" t="n">
-        <v>-225.1932855055664</v>
+        <v>-225.1942038939331</v>
       </c>
     </row>
     <row r="55">
@@ -2181,7 +2181,7 @@
         <v>-0.570097279828427</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.5710735321044922</v>
+        <v>-0.5701582431793213</v>
       </c>
       <c r="F55" t="n">
         <v>-225.19639428</v>
@@ -2190,7 +2190,7 @@
         <v>-224.62629638</v>
       </c>
       <c r="H55" t="n">
-        <v>-225.1973699121045</v>
+        <v>-225.1964546231793</v>
       </c>
     </row>
     <row r="56">
@@ -2213,7 +2213,7 @@
         <v>-0.5716586770979002</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.5697828531265259</v>
+        <v>-0.5711084604263306</v>
       </c>
       <c r="F56" t="n">
         <v>-225.21572392</v>
@@ -2222,7 +2222,7 @@
         <v>-224.64406715</v>
       </c>
       <c r="H56" t="n">
-        <v>-225.2138500031265</v>
+        <v>-225.2151756104263</v>
       </c>
     </row>
     <row r="57">
@@ -2245,7 +2245,7 @@
         <v>-0.602009184853148</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.5970628261566162</v>
+        <v>-0.5971513390541077</v>
       </c>
       <c r="F57" t="n">
         <v>-225.15051444</v>
@@ -2254,7 +2254,7 @@
         <v>-224.54850414</v>
       </c>
       <c r="H57" t="n">
-        <v>-225.1455669661566</v>
+        <v>-225.1456554790541</v>
       </c>
     </row>
     <row r="58">
@@ -2277,7 +2277,7 @@
         <v>-0.5721107659655976</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.5714997053146362</v>
+        <v>-0.5724917650222778</v>
       </c>
       <c r="F58" t="n">
         <v>-225.21743912</v>
@@ -2286,7 +2286,7 @@
         <v>-224.64532755</v>
       </c>
       <c r="H58" t="n">
-        <v>-225.2168272553146</v>
+        <v>-225.2178193150223</v>
       </c>
     </row>
     <row r="59">
@@ -2309,7 +2309,7 @@
         <v>-0.5734403071598115</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.5731257200241089</v>
+        <v>-0.5727307796478271</v>
       </c>
       <c r="F59" t="n">
         <v>-225.22147561</v>
@@ -2318,7 +2318,7 @@
         <v>-224.64803543</v>
       </c>
       <c r="H59" t="n">
-        <v>-225.2211611500241</v>
+        <v>-225.2207662096478</v>
       </c>
     </row>
     <row r="60">
@@ -2341,7 +2341,7 @@
         <v>-0.5739597165988792</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.5771965980529785</v>
+        <v>-0.5767316818237305</v>
       </c>
       <c r="F60" t="n">
         <v>-225.22264704</v>
@@ -2350,7 +2350,7 @@
         <v>-224.64868683</v>
       </c>
       <c r="H60" t="n">
-        <v>-225.225883428053</v>
+        <v>-225.2254185118237</v>
       </c>
     </row>
     <row r="61">
@@ -2373,7 +2373,7 @@
         <v>-0.6106681100233369</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.6078657507896423</v>
+        <v>-0.6090700030326843</v>
       </c>
       <c r="F61" t="n">
         <v>-225.15425197</v>
@@ -2382,7 +2382,7 @@
         <v>-224.54358377</v>
       </c>
       <c r="H61" t="n">
-        <v>-225.1514495207896</v>
+        <v>-225.1526537730327</v>
       </c>
     </row>
     <row r="62">
@@ -2405,7 +2405,7 @@
         <v>-0.6027161047764253</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.6022036671638489</v>
+        <v>-0.6027530431747437</v>
       </c>
       <c r="F62" t="n">
         <v>-225.15081104</v>
@@ -2414,7 +2414,7 @@
         <v>-224.54809459</v>
       </c>
       <c r="H62" t="n">
-        <v>-225.1502982571639</v>
+        <v>-225.1508476331747</v>
       </c>
     </row>
     <row r="63">
@@ -2437,7 +2437,7 @@
         <v>-0.600587899241156</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.5986882448196411</v>
+        <v>-0.5984454154968262</v>
       </c>
       <c r="F63" t="n">
         <v>-225.14992097</v>
@@ -2446,7 +2446,7 @@
         <v>-224.54933255</v>
       </c>
       <c r="H63" t="n">
-        <v>-225.1480207948196</v>
+        <v>-225.1477779654968</v>
       </c>
     </row>
     <row r="64">
@@ -2469,7 +2469,7 @@
         <v>-0.5700181423672994</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.5718231201171875</v>
+        <v>-0.5716156363487244</v>
       </c>
       <c r="F64" t="n">
         <v>-225.19829638</v>
@@ -2478,7 +2478,7 @@
         <v>-224.62828089</v>
       </c>
       <c r="H64" t="n">
-        <v>-225.2001040101172</v>
+        <v>-225.1998965263487</v>
       </c>
     </row>
     <row r="65">
@@ -2501,7 +2501,7 @@
         <v>-0.61708128011385</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.6164752244949341</v>
+        <v>-0.6136215925216675</v>
       </c>
       <c r="F65" t="n">
         <v>-225.15674729</v>
@@ -2510,7 +2510,7 @@
         <v>-224.53966965</v>
       </c>
       <c r="H65" t="n">
-        <v>-225.1561448744949</v>
+        <v>-225.1532912425217</v>
       </c>
     </row>
     <row r="66">
@@ -2533,7 +2533,7 @@
         <v>-0.6030718311446317</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.6033872961997986</v>
+        <v>-0.6028209328651428</v>
       </c>
       <c r="F66" t="n">
         <v>-225.15095946</v>
@@ -2542,7 +2542,7 @@
         <v>-224.54789071</v>
       </c>
       <c r="H66" t="n">
-        <v>-225.1512780061998</v>
+        <v>-225.1507116428651</v>
       </c>
     </row>
     <row r="67">
@@ -2565,7 +2565,7 @@
         <v>-0.5701550474627777</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.5707939863204956</v>
+        <v>-0.5707758665084839</v>
       </c>
       <c r="F67" t="n">
         <v>-225.19510915</v>
@@ -2574,7 +2574,7 @@
         <v>-224.62495396</v>
       </c>
       <c r="H67" t="n">
-        <v>-225.1957479463205</v>
+        <v>-225.1957298265085</v>
       </c>
     </row>
     <row r="68">
@@ -2597,7 +2597,7 @@
         <v>-0.6042989241158059</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.602656364440918</v>
+        <v>-0.6041271090507507</v>
       </c>
       <c r="F68" t="n">
         <v>-225.15148204</v>
@@ -2606,7 +2606,7 @@
         <v>-224.54718044</v>
       </c>
       <c r="H68" t="n">
-        <v>-225.1498368044409</v>
+        <v>-225.1513075490508</v>
       </c>
     </row>
     <row r="69">
@@ -2629,7 +2629,7 @@
         <v>-0.5699629376079556</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.5759601593017578</v>
+        <v>-0.5687477588653564</v>
       </c>
       <c r="F69" t="n">
         <v>-225.2079299</v>
@@ -2638,7 +2638,7 @@
         <v>-224.63796682</v>
       </c>
       <c r="H69" t="n">
-        <v>-225.2139269793018</v>
+        <v>-225.2067145788654</v>
       </c>
     </row>
     <row r="70">
@@ -2661,7 +2661,7 @@
         <v>-0.6182970009435351</v>
       </c>
       <c r="E70" t="n">
-        <v>-0.6183921694755554</v>
+        <v>-0.6170307397842407</v>
       </c>
       <c r="F70" t="n">
         <v>-225.15713969</v>
@@ -2670,7 +2670,7 @@
         <v>-224.53883864</v>
       </c>
       <c r="H70" t="n">
-        <v>-225.1572308094755</v>
+        <v>-225.1558693797842</v>
       </c>
     </row>
     <row r="71">
@@ -2693,7 +2693,7 @@
         <v>-0.571289132637905</v>
       </c>
       <c r="E71" t="n">
-        <v>-0.5681178569793701</v>
+        <v>-0.5698676109313965</v>
       </c>
       <c r="F71" t="n">
         <v>-225.2142136</v>
@@ -2702,7 +2702,7 @@
         <v>-224.64292486</v>
       </c>
       <c r="H71" t="n">
-        <v>-225.2110427169794</v>
+        <v>-225.2127924709314</v>
       </c>
     </row>
     <row r="72">
@@ -2725,7 +2725,7 @@
         <v>-0.5709144969093958</v>
       </c>
       <c r="E72" t="n">
-        <v>-0.5694504976272583</v>
+        <v>-0.5689055919647217</v>
       </c>
       <c r="F72" t="n">
         <v>-225.18012595</v>
@@ -2734,7 +2734,7 @@
         <v>-224.60921028</v>
       </c>
       <c r="H72" t="n">
-        <v>-225.1786607776273</v>
+        <v>-225.1781158719647</v>
       </c>
     </row>
     <row r="73">
@@ -2757,7 +2757,7 @@
         <v>-0.5993262526434282</v>
       </c>
       <c r="E73" t="n">
-        <v>-0.594886302947998</v>
+        <v>-0.6007907390594482</v>
       </c>
       <c r="F73" t="n">
         <v>-225.14939796</v>
@@ -2766,7 +2766,7 @@
         <v>-224.55006936</v>
       </c>
       <c r="H73" t="n">
-        <v>-225.144955662948</v>
+        <v>-225.1508600990595</v>
       </c>
     </row>
     <row r="74">
@@ -2789,7 +2789,7 @@
         <v>-0.5707972657684939</v>
       </c>
       <c r="E74" t="n">
-        <v>-0.5705192089080811</v>
+        <v>-0.5673353672027588</v>
       </c>
       <c r="F74" t="n">
         <v>-225.18225579</v>
@@ -2798,7 +2798,7 @@
         <v>-224.61145869</v>
       </c>
       <c r="H74" t="n">
-        <v>-225.1819778989081</v>
+        <v>-225.1787940572028</v>
       </c>
     </row>
     <row r="75">
@@ -2821,7 +2821,7 @@
         <v>-0.6053632813307506</v>
       </c>
       <c r="E75" t="n">
-        <v>-0.6027822494506836</v>
+        <v>-0.6040399074554443</v>
       </c>
       <c r="F75" t="n">
         <v>-225.15193714</v>
@@ -2830,7 +2830,7 @@
         <v>-224.54657327</v>
       </c>
       <c r="H75" t="n">
-        <v>-225.1493555194507</v>
+        <v>-225.1506131774555</v>
       </c>
     </row>
     <row r="76">
@@ -2853,7 +2853,7 @@
         <v>-0.6113123911540623</v>
       </c>
       <c r="E76" t="n">
-        <v>-0.6119004487991333</v>
+        <v>-0.6124316453933716</v>
       </c>
       <c r="F76" t="n">
         <v>-225.15452988</v>
@@ -2862,7 +2862,7 @@
         <v>-224.54321715</v>
       </c>
       <c r="H76" t="n">
-        <v>-225.1551175987991</v>
+        <v>-225.1556487953934</v>
       </c>
     </row>
     <row r="77">
@@ -2885,7 +2885,7 @@
         <v>-0.6145143590830719</v>
       </c>
       <c r="E77" t="n">
-        <v>-0.6113966703414917</v>
+        <v>-0.6115591526031494</v>
       </c>
       <c r="F77" t="n">
         <v>-225.15583215</v>
@@ -2894,7 +2894,7 @@
         <v>-224.5413217</v>
       </c>
       <c r="H77" t="n">
-        <v>-225.1527183703415</v>
+        <v>-225.1528808526031</v>
       </c>
     </row>
     <row r="78">
@@ -2917,7 +2917,7 @@
         <v>-0.5693785978160539</v>
       </c>
       <c r="E78" t="n">
-        <v>-0.5714067816734314</v>
+        <v>-0.5663788318634033</v>
       </c>
       <c r="F78" t="n">
         <v>-225.21652138</v>
@@ -2926,7 +2926,7 @@
         <v>-224.64714178</v>
       </c>
       <c r="H78" t="n">
-        <v>-225.2185485616734</v>
+        <v>-225.2135206118634</v>
       </c>
     </row>
     <row r="79">
@@ -2949,7 +2949,7 @@
         <v>-0.6046524934414421</v>
       </c>
       <c r="E79" t="n">
-        <v>-0.6040990948677063</v>
+        <v>-0.6043714284896851</v>
       </c>
       <c r="F79" t="n">
         <v>-225.15163323</v>
@@ -2958,7 +2958,7 @@
         <v>-224.54697793</v>
       </c>
       <c r="H79" t="n">
-        <v>-225.1510770248677</v>
+        <v>-225.1513493584897</v>
       </c>
     </row>
     <row r="80">
@@ -2981,7 +2981,7 @@
         <v>-0.5727141876153088</v>
       </c>
       <c r="E80" t="n">
-        <v>-0.5750905275344849</v>
+        <v>-0.5724811553955078</v>
       </c>
       <c r="F80" t="n">
         <v>-225.15357967</v>
@@ -2990,7 +2990,7 @@
         <v>-224.58086525</v>
       </c>
       <c r="H80" t="n">
-        <v>-225.1559557775345</v>
+        <v>-225.1533464053955</v>
       </c>
     </row>
     <row r="81">
@@ -3013,7 +3013,7 @@
         <v>-0.574170889200288</v>
       </c>
       <c r="E81" t="n">
-        <v>-0.5758597850799561</v>
+        <v>-0.5746787786483765</v>
       </c>
       <c r="F81" t="n">
         <v>-225.13735916</v>
@@ -3022,7 +3022,7 @@
         <v>-224.56318747</v>
       </c>
       <c r="H81" t="n">
-        <v>-225.13904725508</v>
+        <v>-225.1378662486484</v>
       </c>
     </row>
     <row r="82">
@@ -3045,7 +3045,7 @@
         <v>-0.6153916607679573</v>
       </c>
       <c r="E82" t="n">
-        <v>-0.6143137216567993</v>
+        <v>-0.6153700351715088</v>
       </c>
       <c r="F82" t="n">
         <v>-225.15616167</v>
@@ -3054,7 +3054,7 @@
         <v>-224.54076713</v>
       </c>
       <c r="H82" t="n">
-        <v>-225.1550808516568</v>
+        <v>-225.1561371651715</v>
       </c>
     </row>
     <row r="83">
@@ -3077,7 +3077,7 @@
         <v>-0.5723464352869472</v>
       </c>
       <c r="E83" t="n">
-        <v>-0.5720179080963135</v>
+        <v>-0.5713894367218018</v>
       </c>
       <c r="F83" t="n">
         <v>-225.15832493</v>
@@ -3086,7 +3086,7 @@
         <v>-224.5859796</v>
       </c>
       <c r="H83" t="n">
-        <v>-225.1579975080963</v>
+        <v>-225.1573690367218</v>
       </c>
     </row>
     <row r="84">
@@ -3109,7 +3109,7 @@
         <v>-0.5749621654174535</v>
       </c>
       <c r="E84" t="n">
-        <v>-0.5748738050460815</v>
+        <v>-0.5786171555519104</v>
       </c>
       <c r="F84" t="n">
         <v>-225.12993067</v>
@@ -3118,7 +3118,7 @@
         <v>-224.55496841</v>
       </c>
       <c r="H84" t="n">
-        <v>-225.1298422150461</v>
+        <v>-225.1335855655519</v>
       </c>
     </row>
     <row r="85">
@@ -3141,7 +3141,7 @@
         <v>-0.6071655569781292</v>
       </c>
       <c r="E85" t="n">
-        <v>-0.6088938117027283</v>
+        <v>-0.6091208457946777</v>
       </c>
       <c r="F85" t="n">
         <v>-225.15271825</v>
@@ -3150,7 +3150,7 @@
         <v>-224.54555284</v>
       </c>
       <c r="H85" t="n">
-        <v>-225.1544466517027</v>
+        <v>-225.1546736857947</v>
       </c>
     </row>
     <row r="86">
@@ -3173,7 +3173,7 @@
         <v>-0.6167213750757807</v>
       </c>
       <c r="E86" t="n">
-        <v>-0.6200075149536133</v>
+        <v>-0.6160931587219238</v>
       </c>
       <c r="F86" t="n">
         <v>-225.15662651</v>
@@ -3182,7 +3182,7 @@
         <v>-224.53990926</v>
       </c>
       <c r="H86" t="n">
-        <v>-225.1599167749536</v>
+        <v>-225.1560024187219</v>
       </c>
     </row>
     <row r="87">
@@ -3205,7 +3205,7 @@
         <v>-0.6124502052525482</v>
       </c>
       <c r="E87" t="n">
-        <v>-0.6131847500801086</v>
+        <v>-0.6109107136726379</v>
       </c>
       <c r="F87" t="n">
         <v>-225.15501117</v>
@@ -3214,7 +3214,7 @@
         <v>-224.54255773</v>
       </c>
       <c r="H87" t="n">
-        <v>-225.1557424800801</v>
+        <v>-225.1534684436726</v>
       </c>
     </row>
     <row r="88">
@@ -3237,7 +3237,7 @@
         <v>-0.5696456858366026</v>
       </c>
       <c r="E88" t="n">
-        <v>-0.5684387683868408</v>
+        <v>-0.5695483088493347</v>
       </c>
       <c r="F88" t="n">
         <v>-225.20789917</v>
@@ -3246,7 +3246,7 @@
         <v>-224.63825557</v>
       </c>
       <c r="H88" t="n">
-        <v>-225.2066943383869</v>
+        <v>-225.2078038788493</v>
       </c>
     </row>
     <row r="89">
@@ -3269,7 +3269,7 @@
         <v>-0.5706454174431665</v>
       </c>
       <c r="E89" t="n">
-        <v>-0.5721858739852905</v>
+        <v>-0.5711344480514526</v>
       </c>
       <c r="F89" t="n">
         <v>-225.18505452</v>
@@ -3278,7 +3278,7 @@
         <v>-224.61440786</v>
       </c>
       <c r="H89" t="n">
-        <v>-225.1865937339853</v>
+        <v>-225.1855423080515</v>
       </c>
     </row>
     <row r="90">
@@ -3301,7 +3301,7 @@
         <v>-0.5694341847206625</v>
       </c>
       <c r="E90" t="n">
-        <v>-0.5715665221214294</v>
+        <v>-0.5695850849151611</v>
       </c>
       <c r="F90" t="n">
         <v>-225.21446314</v>
@@ -3310,7 +3310,7 @@
         <v>-224.64502749</v>
       </c>
       <c r="H90" t="n">
-        <v>-225.2165940121214</v>
+        <v>-225.2146125749152</v>
       </c>
     </row>
     <row r="91">
@@ -3333,7 +3333,7 @@
         <v>-0.5714878036746867</v>
       </c>
       <c r="E91" t="n">
-        <v>-0.5710164308547974</v>
+        <v>-0.5713409781455994</v>
       </c>
       <c r="F91" t="n">
         <v>-225.17060927</v>
@@ -3342,7 +3342,7 @@
         <v>-224.59911953</v>
       </c>
       <c r="H91" t="n">
-        <v>-225.1701359608548</v>
+        <v>-225.1704605081456</v>
       </c>
     </row>
     <row r="92">
@@ -3365,7 +3365,7 @@
         <v>-0.5702750042022141</v>
       </c>
       <c r="E92" t="n">
-        <v>-0.5706355571746826</v>
+        <v>-0.5725454092025757</v>
       </c>
       <c r="F92" t="n">
         <v>-225.19249851</v>
@@ -3374,7 +3374,7 @@
         <v>-224.62222307</v>
       </c>
       <c r="H92" t="n">
-        <v>-225.1928586271747</v>
+        <v>-225.1947684792026</v>
       </c>
     </row>
     <row r="93">
@@ -3397,7 +3397,7 @@
         <v>-0.5693304828221545</v>
       </c>
       <c r="E93" t="n">
-        <v>-0.5650938749313354</v>
+        <v>-0.5664321780204773</v>
       </c>
       <c r="F93" t="n">
         <v>-225.21851198</v>
@@ -3406,7 +3406,7 @@
         <v>-224.64918242</v>
       </c>
       <c r="H93" t="n">
-        <v>-225.2142762949313</v>
+        <v>-225.2156145980205</v>
       </c>
     </row>
     <row r="94">
@@ -3429,7 +3429,7 @@
         <v>-0.5723813828782566</v>
       </c>
       <c r="E94" t="n">
-        <v>-0.5736877918243408</v>
+        <v>-0.5721160173416138</v>
       </c>
       <c r="F94" t="n">
         <v>-225.21837756</v>
@@ -3438,7 +3438,7 @@
         <v>-224.64599605</v>
       </c>
       <c r="H94" t="n">
-        <v>-225.2196838418243</v>
+        <v>-225.2181120673416</v>
       </c>
     </row>
     <row r="95">
@@ -3461,7 +3461,7 @@
         <v>-0.5759628644319013</v>
       </c>
       <c r="E95" t="n">
-        <v>-0.5799564719200134</v>
+        <v>-0.5801811814308167</v>
       </c>
       <c r="F95" t="n">
         <v>-225.121657</v>
@@ -3470,7 +3470,7 @@
         <v>-224.54569639</v>
       </c>
       <c r="H95" t="n">
-        <v>-225.12565286192</v>
+        <v>-225.1258775714308</v>
       </c>
     </row>
     <row r="96">
@@ -3493,7 +3493,7 @@
         <v>-0.6064389951454785</v>
       </c>
       <c r="E96" t="n">
-        <v>-0.6082661151885986</v>
+        <v>-0.6063416004180908</v>
       </c>
       <c r="F96" t="n">
         <v>-225.15240159</v>
@@ -3502,7 +3502,7 @@
         <v>-224.54596298</v>
       </c>
       <c r="H96" t="n">
-        <v>-225.1542290951886</v>
+        <v>-225.1523045804181</v>
       </c>
     </row>
     <row r="97">
@@ -3525,7 +3525,7 @@
         <v>-0.5698148022596347</v>
       </c>
       <c r="E97" t="n">
-        <v>-0.5696210861206055</v>
+        <v>-0.5708622336387634</v>
       </c>
       <c r="F97" t="n">
         <v>-225.20321446</v>
@@ -3534,7 +3534,7 @@
         <v>-224.63339885</v>
       </c>
       <c r="H97" t="n">
-        <v>-225.2030199361206</v>
+        <v>-225.2042610836388</v>
       </c>
     </row>
     <row r="98">
@@ -3557,7 +3557,7 @@
         <v>-0.5711938697833618</v>
       </c>
       <c r="E98" t="n">
-        <v>-0.5670121908187866</v>
+        <v>-0.5693700313568115</v>
       </c>
       <c r="F98" t="n">
         <v>-225.21381632</v>
@@ -3566,7 +3566,7 @@
         <v>-224.64262054</v>
       </c>
       <c r="H98" t="n">
-        <v>-225.2096327308188</v>
+        <v>-225.2119905713568</v>
       </c>
     </row>
     <row r="99">
@@ -3589,7 +3589,7 @@
         <v>-0.573253930451681</v>
       </c>
       <c r="E99" t="n">
-        <v>-0.5769002437591553</v>
+        <v>-0.5754450559616089</v>
       </c>
       <c r="F99" t="n">
         <v>-225.14715646</v>
@@ -3598,7 +3598,7 @@
         <v>-224.57390382</v>
       </c>
       <c r="H99" t="n">
-        <v>-225.1508040637592</v>
+        <v>-225.1493488759616</v>
       </c>
     </row>
     <row r="100">
@@ -3621,7 +3621,7 @@
         <v>-0.5711047836955625</v>
       </c>
       <c r="E100" t="n">
-        <v>-0.5684516429901123</v>
+        <v>-0.5692117214202881</v>
       </c>
       <c r="F100" t="n">
         <v>-225.21341154</v>
@@ -3630,7 +3630,7 @@
         <v>-224.64230892</v>
       </c>
       <c r="H100" t="n">
-        <v>-225.2107605629901</v>
+        <v>-225.2115206414203</v>
       </c>
     </row>
     <row r="101">
@@ -3653,7 +3653,7 @@
         <v>-0.5736148755044511</v>
       </c>
       <c r="E101" t="n">
-        <v>-0.5750607252120972</v>
+        <v>-0.5731390118598938</v>
       </c>
       <c r="F101" t="n">
         <v>-225.22189339</v>
@@ -3662,7 +3662,7 @@
         <v>-224.64827932</v>
       </c>
       <c r="H101" t="n">
-        <v>-225.2233400452121</v>
+        <v>-225.2214183318599</v>
       </c>
     </row>
     <row r="102">
@@ -3685,7 +3685,7 @@
         <v>-0.614238516973628</v>
       </c>
       <c r="E102" t="n">
-        <v>-0.6119942665100098</v>
+        <v>-0.6134811639785767</v>
       </c>
       <c r="F102" t="n">
         <v>-225.15572551</v>
@@ -3694,7 +3694,7 @@
         <v>-224.54149278</v>
       </c>
       <c r="H102" t="n">
-        <v>-225.15348704651</v>
+        <v>-225.1549739439786</v>
       </c>
     </row>
     <row r="103">
@@ -3717,7 +3717,7 @@
         <v>-0.5754436602898454</v>
       </c>
       <c r="E103" t="n">
-        <v>-0.5794148445129395</v>
+        <v>-0.5783100128173828</v>
       </c>
       <c r="F103" t="n">
         <v>-225.12579222</v>
@@ -3726,7 +3726,7 @@
         <v>-224.55034783</v>
       </c>
       <c r="H103" t="n">
-        <v>-225.1297626745129</v>
+        <v>-225.1286578428174</v>
       </c>
     </row>
     <row r="104">
@@ -3749,7 +3749,7 @@
         <v>-0.5737697674944229</v>
       </c>
       <c r="E104" t="n">
-        <v>-0.5779474377632141</v>
+        <v>-0.577808141708374</v>
       </c>
       <c r="F104" t="n">
         <v>-225.14146073</v>
@@ -3758,7 +3758,7 @@
         <v>-224.56768941</v>
       </c>
       <c r="H104" t="n">
-        <v>-225.1456368477632</v>
+        <v>-225.1454975517084</v>
       </c>
     </row>
     <row r="105">
@@ -3781,7 +3781,7 @@
         <v>-0.6000509093344109</v>
       </c>
       <c r="E105" t="n">
-        <v>-0.600739598274231</v>
+        <v>-0.6013756990432739</v>
       </c>
       <c r="F105" t="n">
         <v>-225.14969735</v>
@@ -3790,7 +3790,7 @@
         <v>-224.54964694</v>
       </c>
       <c r="H105" t="n">
-        <v>-225.1503865382742</v>
+        <v>-225.1510226390433</v>
       </c>
     </row>
     <row r="106">
@@ -3813,7 +3813,7 @@
         <v>-0.5727793333099318</v>
       </c>
       <c r="E106" t="n">
-        <v>-0.5741517543792725</v>
+        <v>-0.5739165544509888</v>
       </c>
       <c r="F106" t="n">
         <v>-225.15278258</v>
@@ -3822,7 +3822,7 @@
         <v>-224.58000388</v>
       </c>
       <c r="H106" t="n">
-        <v>-225.1541556343793</v>
+        <v>-225.153920434451</v>
       </c>
     </row>
     <row r="107">
@@ -3845,7 +3845,7 @@
         <v>-0.5695348543798451</v>
       </c>
       <c r="E107" t="n">
-        <v>-0.5711395144462585</v>
+        <v>-0.5695717334747314</v>
       </c>
       <c r="F107" t="n">
         <v>-225.21125261</v>
@@ -3854,7 +3854,7 @@
         <v>-224.64172038</v>
       </c>
       <c r="H107" t="n">
-        <v>-225.2128598944463</v>
+        <v>-225.2112921134747</v>
       </c>
     </row>
     <row r="108">
@@ -3877,7 +3877,7 @@
         <v>-0.6096466975472871</v>
       </c>
       <c r="E108" t="n">
-        <v>-0.6111751794815063</v>
+        <v>-0.6088639497756958</v>
       </c>
       <c r="F108" t="n">
         <v>-225.15380487</v>
@@ -3886,7 +3886,7 @@
         <v>-224.54416183</v>
       </c>
       <c r="H108" t="n">
-        <v>-225.1553370094815</v>
+        <v>-225.1530257797757</v>
       </c>
     </row>
     <row r="109">
@@ -3909,7 +3909,7 @@
         <v>-0.6094432636128024</v>
       </c>
       <c r="E109" t="n">
-        <v>-0.6089580059051514</v>
+        <v>-0.6074683666229248</v>
       </c>
       <c r="F109" t="n">
         <v>-225.15371747</v>
@@ -3918,7 +3918,7 @@
         <v>-224.54427376</v>
       </c>
       <c r="H109" t="n">
-        <v>-225.1532317659052</v>
+        <v>-225.1517421266229</v>
       </c>
     </row>
     <row r="110">
@@ -3941,7 +3941,7 @@
         <v>-0.5700441232979128</v>
       </c>
       <c r="E110" t="n">
-        <v>-0.5709322094917297</v>
+        <v>-0.570531964302063</v>
       </c>
       <c r="F110" t="n">
         <v>-225.19766569</v>
@@ -3950,7 +3950,7 @@
         <v>-224.62762317</v>
       </c>
       <c r="H110" t="n">
-        <v>-225.1985553794917</v>
+        <v>-225.1981551343021</v>
       </c>
     </row>
     <row r="111">
@@ -3973,7 +3973,7 @@
         <v>-0.571750254754158</v>
       </c>
       <c r="E111" t="n">
-        <v>-0.5709923505783081</v>
+        <v>-0.5716167688369751</v>
       </c>
       <c r="F111" t="n">
         <v>-225.21608252</v>
@@ -3982,7 +3982,7 @@
         <v>-224.64433378</v>
       </c>
       <c r="H111" t="n">
-        <v>-225.2153261305783</v>
+        <v>-225.215950548837</v>
       </c>
     </row>
     <row r="112">
@@ -4005,7 +4005,7 @@
         <v>-0.5717369579303664</v>
       </c>
       <c r="E112" t="n">
-        <v>-0.5705104470252991</v>
+        <v>-0.5725027322769165</v>
       </c>
       <c r="F112" t="n">
         <v>-225.16683339</v>
@@ -4014,7 +4014,7 @@
         <v>-224.59509509</v>
       </c>
       <c r="H112" t="n">
-        <v>-225.1656055370253</v>
+        <v>-225.1675978222769</v>
       </c>
     </row>
     <row r="113">
@@ -4037,7 +4037,7 @@
         <v>-0.5700707730819833</v>
       </c>
       <c r="E113" t="n">
-        <v>-0.5710708498954773</v>
+        <v>-0.5709953308105469</v>
       </c>
       <c r="F113" t="n">
         <v>-225.19703181</v>
@@ -4046,7 +4046,7 @@
         <v>-224.62696185</v>
       </c>
       <c r="H113" t="n">
-        <v>-225.1980326998955</v>
+        <v>-225.1979571808105</v>
       </c>
     </row>
     <row r="114">
@@ -4069,7 +4069,7 @@
         <v>-0.5756482775282076</v>
       </c>
       <c r="E114" t="n">
-        <v>-0.5822665691375732</v>
+        <v>-0.5860288739204407</v>
       </c>
       <c r="F114" t="n">
         <v>-225.12413732</v>
@@ -4078,7 +4078,7 @@
         <v>-224.54849067</v>
       </c>
       <c r="H114" t="n">
-        <v>-225.1307572391376</v>
+        <v>-225.1345195439204</v>
       </c>
     </row>
     <row r="115">
@@ -4101,7 +4101,7 @@
         <v>-0.5714727440454934</v>
       </c>
       <c r="E115" t="n">
-        <v>-0.5678619146347046</v>
+        <v>-0.5699681043624878</v>
       </c>
       <c r="F115" t="n">
         <v>-225.21498436</v>
@@ -4110,7 +4110,7 @@
         <v>-224.64351124</v>
       </c>
       <c r="H115" t="n">
-        <v>-225.2113731546347</v>
+        <v>-225.2134793443625</v>
       </c>
     </row>
     <row r="116">
@@ -4133,7 +4133,7 @@
         <v>-0.6016587090415922</v>
       </c>
       <c r="E116" t="n">
-        <v>-0.5987859964370728</v>
+        <v>-0.6001286506652832</v>
       </c>
       <c r="F116" t="n">
         <v>-225.15036633</v>
@@ -4142,7 +4142,7 @@
         <v>-224.54871003</v>
       </c>
       <c r="H116" t="n">
-        <v>-225.1474960264371</v>
+        <v>-225.1488386806653</v>
       </c>
     </row>
     <row r="117">
@@ -4165,7 +4165,7 @@
         <v>-0.5715654193381567</v>
       </c>
       <c r="E117" t="n">
-        <v>-0.5685855746269226</v>
+        <v>-0.570063591003418</v>
       </c>
       <c r="F117" t="n">
         <v>-225.21535784</v>
@@ -4174,7 +4174,7 @@
         <v>-224.64379272</v>
       </c>
       <c r="H117" t="n">
-        <v>-225.2123782946269</v>
+        <v>-225.2138563110034</v>
       </c>
     </row>
     <row r="118">
@@ -4197,7 +4197,7 @@
         <v>-0.5736188464240288</v>
       </c>
       <c r="E118" t="n">
-        <v>-0.5758353471755981</v>
+        <v>-0.5743153691291809</v>
       </c>
       <c r="F118" t="n">
         <v>-225.14309446</v>
@@ -4206,7 +4206,7 @@
         <v>-224.56947616</v>
       </c>
       <c r="H118" t="n">
-        <v>-225.1453115071756</v>
+        <v>-225.1437915291292</v>
       </c>
     </row>
     <row r="119">
@@ -4229,7 +4229,7 @@
         <v>-0.6007653811692248</v>
       </c>
       <c r="E119" t="n">
-        <v>-0.5966473817825317</v>
+        <v>-0.5980876684188843</v>
       </c>
       <c r="F119" t="n">
         <v>-225.14999534</v>
@@ -4238,7 +4238,7 @@
         <v>-224.54922831</v>
       </c>
       <c r="H119" t="n">
-        <v>-225.1458756917825</v>
+        <v>-225.1473159784189</v>
       </c>
     </row>
     <row r="120">
@@ -4261,7 +4261,7 @@
         <v>-0.5705391445745658</v>
       </c>
       <c r="E120" t="n">
-        <v>-0.5698004961013794</v>
+        <v>-0.5689977407455444</v>
       </c>
       <c r="F120" t="n">
         <v>-225.21081521</v>
@@ -4270,7 +4270,7 @@
         <v>-224.64027715</v>
       </c>
       <c r="H120" t="n">
-        <v>-225.2100776461014</v>
+        <v>-225.2092748907455</v>
       </c>
     </row>
     <row r="121">
@@ -4293,7 +4293,7 @@
         <v>-0.5722943947915655</v>
       </c>
       <c r="E121" t="n">
-        <v>-0.5740456581115723</v>
+        <v>-0.5733739137649536</v>
       </c>
       <c r="F121" t="n">
         <v>-225.2180722</v>
@@ -4302,7 +4302,7 @@
         <v>-224.64578058</v>
       </c>
       <c r="H121" t="n">
-        <v>-225.2198262381116</v>
+        <v>-225.219154493765</v>
       </c>
     </row>
     <row r="122">
@@ -4325,7 +4325,7 @@
         <v>-0.5702453753506271</v>
       </c>
       <c r="E122" t="n">
-        <v>-0.5702845454216003</v>
+        <v>-0.5710334777832031</v>
       </c>
       <c r="F122" t="n">
         <v>-225.19315609</v>
@@ -4334,7 +4334,7 @@
         <v>-224.62291141</v>
       </c>
       <c r="H122" t="n">
-        <v>-225.1931959554216</v>
+        <v>-225.1939448877832</v>
       </c>
     </row>
     <row r="123">
@@ -4357,7 +4357,7 @@
         <v>-0.5749033249091441</v>
       </c>
       <c r="E123" t="n">
-        <v>-0.5710223317146301</v>
+        <v>-0.5765591859817505</v>
       </c>
       <c r="F123" t="n">
         <v>-225.22417974</v>
@@ -4366,7 +4366,7 @@
         <v>-224.64927643</v>
       </c>
       <c r="H123" t="n">
-        <v>-225.2202987617146</v>
+        <v>-225.2258356159817</v>
       </c>
     </row>
     <row r="124">
@@ -4389,7 +4389,7 @@
         <v>-0.6131837719893145</v>
       </c>
       <c r="E124" t="n">
-        <v>-0.6137118339538574</v>
+        <v>-0.6095388531684875</v>
       </c>
       <c r="F124" t="n">
         <v>-225.15531095</v>
@@ -4398,7 +4398,7 @@
         <v>-224.5421262</v>
       </c>
       <c r="H124" t="n">
-        <v>-225.1558380339539</v>
+        <v>-225.1516650531685</v>
       </c>
     </row>
     <row r="125">
@@ -4421,7 +4421,7 @@
         <v>-0.603774980312507</v>
       </c>
       <c r="E125" t="n">
-        <v>-0.6009255647659302</v>
+        <v>-0.6015470027923584</v>
       </c>
       <c r="F125" t="n">
         <v>-225.15125737</v>
@@ -4430,7 +4430,7 @@
         <v>-224.54748425</v>
       </c>
       <c r="H125" t="n">
-        <v>-225.1484098147659</v>
+        <v>-225.1490312527924</v>
       </c>
     </row>
     <row r="126">
@@ -4453,7 +4453,7 @@
         <v>-0.6147989761067133</v>
       </c>
       <c r="E126" t="n">
-        <v>-0.6098518371582031</v>
+        <v>-0.6118628978729248</v>
       </c>
       <c r="F126" t="n">
         <v>-225.15594012</v>
@@ -4462,7 +4462,7 @@
         <v>-224.54114424</v>
       </c>
       <c r="H126" t="n">
-        <v>-225.1509960771582</v>
+        <v>-225.1530071378729</v>
       </c>
     </row>
     <row r="127">
@@ -4485,7 +4485,7 @@
         <v>-0.600946045551721</v>
       </c>
       <c r="E127" t="n">
-        <v>-0.5991393327713013</v>
+        <v>-0.6005540490150452</v>
       </c>
       <c r="F127" t="n">
         <v>-225.1500697</v>
@@ -4494,7 +4494,7 @@
         <v>-224.54912407</v>
       </c>
       <c r="H127" t="n">
-        <v>-225.1482634027713</v>
+        <v>-225.1496781190151</v>
       </c>
     </row>
     <row r="128">
@@ -4517,7 +4517,7 @@
         <v>-0.5747338104517342</v>
       </c>
       <c r="E128" t="n">
-        <v>-0.5685631036758423</v>
+        <v>-0.568917453289032</v>
       </c>
       <c r="F128" t="n">
         <v>-225.22395824</v>
@@ -4526,7 +4526,7 @@
         <v>-224.64922565</v>
       </c>
       <c r="H128" t="n">
-        <v>-225.2177887536758</v>
+        <v>-225.218143103289</v>
       </c>
     </row>
     <row r="129">
@@ -4549,7 +4549,7 @@
         <v>-0.5703693185812952</v>
       </c>
       <c r="E129" t="n">
-        <v>-0.570879340171814</v>
+        <v>-0.5711685419082642</v>
       </c>
       <c r="F129" t="n">
         <v>-225.19050637</v>
@@ -4558,7 +4558,7 @@
         <v>-224.62013573</v>
       </c>
       <c r="H129" t="n">
-        <v>-225.1910150701718</v>
+        <v>-225.1913042719083</v>
       </c>
     </row>
     <row r="130">
@@ -4581,7 +4581,7 @@
         <v>-0.5702140057653566</v>
       </c>
       <c r="E130" t="n">
-        <v>-0.5707132816314697</v>
+        <v>-0.5703879594802856</v>
       </c>
       <c r="F130" t="n">
         <v>-225.19381029</v>
@@ -4590,7 +4590,7 @@
         <v>-224.62359591</v>
       </c>
       <c r="H130" t="n">
-        <v>-225.1943091916315</v>
+        <v>-225.1939838694803</v>
       </c>
     </row>
     <row r="131">
@@ -4613,7 +4613,7 @@
         <v>-0.5743893535247506</v>
       </c>
       <c r="E131" t="n">
-        <v>-0.5757675766944885</v>
+        <v>-0.5713911056518555</v>
       </c>
       <c r="F131" t="n">
         <v>-225.22343999</v>
@@ -4622,7 +4622,7 @@
         <v>-224.64904981</v>
       </c>
       <c r="H131" t="n">
-        <v>-225.2248173866945</v>
+        <v>-225.2204409156519</v>
       </c>
     </row>
     <row r="132">
@@ -4645,7 +4645,7 @@
         <v>-0.569419618674377</v>
       </c>
       <c r="E132" t="n">
-        <v>-0.5728602409362793</v>
+        <v>-0.5708320736885071</v>
       </c>
       <c r="F132" t="n">
         <v>-225.21498399</v>
@@ -4654,7 +4654,7 @@
         <v>-224.64556302</v>
       </c>
       <c r="H132" t="n">
-        <v>-225.2184232609363</v>
+        <v>-225.2163950936885</v>
       </c>
     </row>
     <row r="133">
@@ -4677,7 +4677,7 @@
         <v>-0.6014800364725927</v>
       </c>
       <c r="E133" t="n">
-        <v>-0.5976276397705078</v>
+        <v>-0.6011637449264526</v>
       </c>
       <c r="F133" t="n">
         <v>-225.15029228</v>
@@ -4686,7 +4686,7 @@
         <v>-224.54881328</v>
       </c>
       <c r="H133" t="n">
-        <v>-225.1464409197705</v>
+        <v>-225.1499770249264</v>
       </c>
     </row>
     <row r="134">
@@ -4709,7 +4709,7 @@
         <v>-0.6058986995177409</v>
       </c>
       <c r="E134" t="n">
-        <v>-0.6085178852081299</v>
+        <v>-0.6073151826858521</v>
       </c>
       <c r="F134" t="n">
         <v>-225.15216767</v>
@@ -4718,7 +4718,7 @@
         <v>-224.546269</v>
       </c>
       <c r="H134" t="n">
-        <v>-225.1547868852081</v>
+        <v>-225.1535841826858</v>
       </c>
     </row>
     <row r="135">
@@ -4741,7 +4741,7 @@
         <v>-0.5705051138944942</v>
       </c>
       <c r="E135" t="n">
-        <v>-0.5718700885772705</v>
+        <v>-0.5687131881713867</v>
       </c>
       <c r="F135" t="n">
         <v>-225.18780554</v>
@@ -4750,7 +4750,7 @@
         <v>-224.61730102</v>
       </c>
       <c r="H135" t="n">
-        <v>-225.1891711085773</v>
+        <v>-225.1860142081714</v>
       </c>
     </row>
     <row r="136">
@@ -4773,7 +4773,7 @@
         <v>-0.6100450465431565</v>
       </c>
       <c r="E136" t="n">
-        <v>-0.6107330322265625</v>
+        <v>-0.6098556518554688</v>
       </c>
       <c r="F136" t="n">
         <v>-225.15398139</v>
@@ -4782,7 +4782,7 @@
         <v>-224.54393509</v>
       </c>
       <c r="H136" t="n">
-        <v>-225.1546681222266</v>
+        <v>-225.1537907418555</v>
       </c>
     </row>
     <row r="137">
@@ -4805,7 +4805,7 @@
         <v>-0.5718953770342259</v>
       </c>
       <c r="E137" t="n">
-        <v>-0.5676793456077576</v>
+        <v>-0.5699311494827271</v>
       </c>
       <c r="F137" t="n">
         <v>-225.16453933</v>
@@ -4814,7 +4814,7 @@
         <v>-224.59264381</v>
       </c>
       <c r="H137" t="n">
-        <v>-225.1603231556078</v>
+        <v>-225.1625749594827</v>
       </c>
     </row>
     <row r="138">
@@ -4837,7 +4837,7 @@
         <v>-0.5695186566257783</v>
       </c>
       <c r="E138" t="n">
-        <v>-0.5719809532165527</v>
+        <v>-0.5700047016143799</v>
       </c>
       <c r="F138" t="n">
         <v>-225.21179773</v>
@@ -4846,7 +4846,7 @@
         <v>-224.64228257</v>
       </c>
       <c r="H138" t="n">
-        <v>-225.2142635232165</v>
+        <v>-225.2122872716144</v>
       </c>
     </row>
     <row r="139">
@@ -4869,7 +4869,7 @@
         <v>-0.607909554448238</v>
       </c>
       <c r="E139" t="n">
-        <v>-0.6072890162467957</v>
+        <v>-0.606000542640686</v>
       </c>
       <c r="F139" t="n">
         <v>-225.15304251</v>
@@ -4878,7 +4878,7 @@
         <v>-224.54513631</v>
       </c>
       <c r="H139" t="n">
-        <v>-225.1524253262468</v>
+        <v>-225.1511368526407</v>
       </c>
     </row>
     <row r="140">
@@ -4901,7 +4901,7 @@
         <v>-0.5991479218428335</v>
       </c>
       <c r="E140" t="n">
-        <v>-0.5962765216827393</v>
+        <v>-0.601340651512146</v>
       </c>
       <c r="F140" t="n">
         <v>-225.14932277</v>
@@ -4910,7 +4910,7 @@
         <v>-224.55017565</v>
       </c>
       <c r="H140" t="n">
-        <v>-225.1464521716827</v>
+        <v>-225.1515163015121</v>
       </c>
     </row>
     <row r="141">
@@ -4933,7 +4933,7 @@
         <v>-0.5743384170212652</v>
       </c>
       <c r="E141" t="n">
-        <v>-0.5749756097793579</v>
+        <v>-0.5753285884857178</v>
       </c>
       <c r="F141" t="n">
         <v>-225.1357127</v>
@@ -4942,7 +4942,7 @@
         <v>-224.56137339</v>
       </c>
       <c r="H141" t="n">
-        <v>-225.1363489997794</v>
+        <v>-225.1367019784857</v>
       </c>
     </row>
     <row r="142">
@@ -4965,7 +4965,7 @@
         <v>-0.6032449940704212</v>
       </c>
       <c r="E142" t="n">
-        <v>-0.6031347513198853</v>
+        <v>-0.601851761341095</v>
       </c>
       <c r="F142" t="n">
         <v>-225.15103385</v>
@@ -4974,7 +4974,7 @@
         <v>-224.54778894</v>
       </c>
       <c r="H142" t="n">
-        <v>-225.1509236913199</v>
+        <v>-225.1496407013411</v>
       </c>
     </row>
     <row r="143">
@@ -4997,7 +4997,7 @@
         <v>-0.5699878168848764</v>
       </c>
       <c r="E143" t="n">
-        <v>-0.5721105337142944</v>
+        <v>-0.5725981593132019</v>
       </c>
       <c r="F143" t="n">
         <v>-225.19892339</v>
@@ -5006,7 +5006,7 @@
         <v>-224.62893443</v>
       </c>
       <c r="H143" t="n">
-        <v>-225.2010449637143</v>
+        <v>-225.2015325893132</v>
       </c>
     </row>
     <row r="144">
@@ -5029,7 +5029,7 @@
         <v>-0.5697475921651269</v>
       </c>
       <c r="E144" t="n">
-        <v>-0.5688357353210449</v>
+        <v>-0.5716654062271118</v>
       </c>
       <c r="F144" t="n">
         <v>-225.20499924</v>
@@ -5038,7 +5038,7 @@
         <v>-224.63525132</v>
       </c>
       <c r="H144" t="n">
-        <v>-225.2040870553211</v>
+        <v>-225.2069167262271</v>
       </c>
     </row>
     <row r="145">
@@ -5061,7 +5061,7 @@
         <v>-0.5695687672589851</v>
       </c>
       <c r="E145" t="n">
-        <v>-0.5688266754150391</v>
+        <v>-0.5687422752380371</v>
       </c>
       <c r="F145" t="n">
         <v>-225.21015053</v>
@@ -5070,7 +5070,7 @@
         <v>-224.64058285</v>
       </c>
       <c r="H145" t="n">
-        <v>-225.209409525415</v>
+        <v>-225.209325125238</v>
       </c>
     </row>
     <row r="146">
@@ -5093,7 +5093,7 @@
         <v>-0.6163704520684232</v>
       </c>
       <c r="E146" t="n">
-        <v>-0.6191110610961914</v>
+        <v>-0.6212543249130249</v>
       </c>
       <c r="F146" t="n">
         <v>-225.15650688</v>
@@ -5102,7 +5102,7 @@
         <v>-224.54013901</v>
       </c>
       <c r="H146" t="n">
-        <v>-225.1592500710962</v>
+        <v>-225.161393334913</v>
       </c>
     </row>
     <row r="147">
@@ -5125,7 +5125,7 @@
         <v>-0.569365141572671</v>
       </c>
       <c r="E147" t="n">
-        <v>-0.5716224908828735</v>
+        <v>-0.5678495764732361</v>
       </c>
       <c r="F147" t="n">
         <v>-225.21702545</v>
@@ -5134,7 +5134,7 @@
         <v>-224.64765896</v>
       </c>
       <c r="H147" t="n">
-        <v>-225.2192814508829</v>
+        <v>-225.2155085364732</v>
       </c>
     </row>
     <row r="148">
@@ -5157,7 +5157,7 @@
         <v>-0.5700579705658719</v>
       </c>
       <c r="E148" t="n">
-        <v>-0.5692163705825806</v>
+        <v>-0.5682219862937927</v>
       </c>
       <c r="F148" t="n">
         <v>-225.20843107</v>
@@ -5166,7 +5166,7 @@
         <v>-224.63837155</v>
       </c>
       <c r="H148" t="n">
-        <v>-225.2075879205826</v>
+        <v>-225.2065935362938</v>
       </c>
     </row>
     <row r="149">
@@ -5189,7 +5189,7 @@
         <v>-0.5706091640160826</v>
       </c>
       <c r="E149" t="n">
-        <v>-0.5716816186904907</v>
+        <v>-0.5703893899917603</v>
       </c>
       <c r="F149" t="n">
         <v>-225.18574678</v>
@@ -5198,7 +5198,7 @@
         <v>-224.61513643</v>
       </c>
       <c r="H149" t="n">
-        <v>-225.1868180486905</v>
+        <v>-225.1855258199918</v>
       </c>
     </row>
     <row r="150">
@@ -5221,7 +5221,7 @@
         <v>-0.59823437805594</v>
       </c>
       <c r="E150" t="n">
-        <v>-0.5947854518890381</v>
+        <v>-0.5956329107284546</v>
       </c>
       <c r="F150" t="n">
         <v>-225.14894389</v>
@@ -5230,7 +5230,7 @@
         <v>-224.55071114</v>
       </c>
       <c r="H150" t="n">
-        <v>-225.145496591889</v>
+        <v>-225.1463440507285</v>
       </c>
     </row>
     <row r="151">
@@ -5253,7 +5253,7 @@
         <v>-0.611531271396224</v>
       </c>
       <c r="E151" t="n">
-        <v>-0.6129459738731384</v>
+        <v>-0.6125285625457764</v>
       </c>
       <c r="F151" t="n">
         <v>-225.15462441</v>
@@ -5262,7 +5262,7 @@
         <v>-224.54309061</v>
       </c>
       <c r="H151" t="n">
-        <v>-225.1560365838731</v>
+        <v>-225.1556191725458</v>
       </c>
     </row>
     <row r="152">
@@ -5285,7 +5285,7 @@
         <v>-0.602541230025824</v>
       </c>
       <c r="E152" t="n">
-        <v>-0.6011897325515747</v>
+        <v>-0.6013208627700806</v>
       </c>
       <c r="F152" t="n">
         <v>-225.15073678</v>
@@ -5294,7 +5294,7 @@
         <v>-224.54819666</v>
       </c>
       <c r="H152" t="n">
-        <v>-225.1493863925516</v>
+        <v>-225.1495175227701</v>
       </c>
     </row>
     <row r="153">
@@ -5317,7 +5317,7 @@
         <v>-0.5761787090160184</v>
       </c>
       <c r="E153" t="n">
-        <v>-0.5811120271682739</v>
+        <v>-0.580887496471405</v>
       </c>
       <c r="F153" t="n">
         <v>-225.12000658</v>
@@ -5326,7 +5326,7 @@
         <v>-224.54382897</v>
       </c>
       <c r="H153" t="n">
-        <v>-225.1249409971683</v>
+        <v>-225.1247164664714</v>
       </c>
     </row>
     <row r="154">
@@ -5349,7 +5349,7 @@
         <v>-0.5745112859426114</v>
       </c>
       <c r="E154" t="n">
-        <v>-0.5743438005447388</v>
+        <v>-0.5758461356163025</v>
       </c>
       <c r="F154" t="n">
         <v>-225.13406289</v>
@@ -5358,7 +5358,7 @@
         <v>-224.55955159</v>
       </c>
       <c r="H154" t="n">
-        <v>-225.1338953905448</v>
+        <v>-225.1353977256163</v>
       </c>
     </row>
     <row r="155">
@@ -5381,7 +5381,7 @@
         <v>-0.5755450847840682</v>
       </c>
       <c r="E155" t="n">
-        <v>-0.5777736306190491</v>
+        <v>-0.5786862373352051</v>
       </c>
       <c r="F155" t="n">
         <v>-225.12496456</v>
@@ -5390,7 +5390,7 @@
         <v>-224.54941959</v>
       </c>
       <c r="H155" t="n">
-        <v>-225.1271932206191</v>
+        <v>-225.1281058273352</v>
       </c>
     </row>
     <row r="156">
@@ -5413,7 +5413,7 @@
         <v>-0.5720035565788646</v>
       </c>
       <c r="E156" t="n">
-        <v>-0.5683062076568604</v>
+        <v>-0.5708075761795044</v>
       </c>
       <c r="F156" t="n">
         <v>-225.16299829</v>
@@ -5422,7 +5422,7 @@
         <v>-224.59099467</v>
       </c>
       <c r="H156" t="n">
-        <v>-225.1593008776568</v>
+        <v>-225.1618022461795</v>
       </c>
     </row>
     <row r="157">
@@ -5445,7 +5445,7 @@
         <v>-0.5698671861104683</v>
       </c>
       <c r="E157" t="n">
-        <v>-0.5731545686721802</v>
+        <v>-0.5717827081680298</v>
       </c>
       <c r="F157" t="n">
         <v>-225.2074206</v>
@@ -5454,7 +5454,7 @@
         <v>-224.63755424</v>
       </c>
       <c r="H157" t="n">
-        <v>-225.2107088086722</v>
+        <v>-225.209336948168</v>
       </c>
     </row>
     <row r="158">
@@ -5477,7 +5477,7 @@
         <v>-0.5744256408985587</v>
       </c>
       <c r="E158" t="n">
-        <v>-0.5754693746566772</v>
+        <v>-0.574899435043335</v>
       </c>
       <c r="F158" t="n">
         <v>-225.13488803</v>
@@ -5486,7 +5486,7 @@
         <v>-224.56046324</v>
       </c>
       <c r="H158" t="n">
-        <v>-225.1359326146567</v>
+        <v>-225.1353626750433</v>
       </c>
     </row>
     <row r="159">
@@ -5509,7 +5509,7 @@
         <v>-0.5748713921920644</v>
       </c>
       <c r="E159" t="n">
-        <v>-0.5764259099960327</v>
+        <v>-0.5775721073150635</v>
       </c>
       <c r="F159" t="n">
         <v>-225.13075805</v>
@@ -5518,7 +5518,7 @@
         <v>-224.55588842</v>
       </c>
       <c r="H159" t="n">
-        <v>-225.132314329996</v>
+        <v>-225.1334605273151</v>
       </c>
     </row>
     <row r="160">
@@ -5541,7 +5541,7 @@
         <v>-0.5693404004621456</v>
       </c>
       <c r="E160" t="n">
-        <v>-0.5671983957290649</v>
+        <v>-0.5654501914978027</v>
       </c>
       <c r="F160" t="n">
         <v>-225.21802077</v>
@@ -5550,7 +5550,7 @@
         <v>-224.6486793</v>
       </c>
       <c r="H160" t="n">
-        <v>-225.2158776957291</v>
+        <v>-225.2141294914978</v>
       </c>
     </row>
     <row r="161">
@@ -5573,7 +5573,7 @@
         <v>-0.5696053936227126</v>
       </c>
       <c r="E161" t="n">
-        <v>-0.5669218897819519</v>
+        <v>-0.5700002312660217</v>
       </c>
       <c r="F161" t="n">
         <v>-225.20903276</v>
@@ -5582,7 +5582,7 @@
         <v>-224.63942797</v>
       </c>
       <c r="H161" t="n">
-        <v>-225.206349859782</v>
+        <v>-225.209428201266</v>
       </c>
     </row>
     <row r="162">
@@ -5605,7 +5605,7 @@
         <v>-0.5696260896749926</v>
       </c>
       <c r="E162" t="n">
-        <v>-0.5678380131721497</v>
+        <v>-0.5690173506736755</v>
       </c>
       <c r="F162" t="n">
         <v>-225.2084679</v>
@@ -5614,7 +5614,7 @@
         <v>-224.63884391</v>
       </c>
       <c r="H162" t="n">
-        <v>-225.2066819231721</v>
+        <v>-225.2078612606737</v>
       </c>
     </row>
     <row r="163">
@@ -5637,7 +5637,7 @@
         <v>-0.5710831502878115</v>
       </c>
       <c r="E163" t="n">
-        <v>-0.5692598819732666</v>
+        <v>-0.5719526410102844</v>
       </c>
       <c r="F163" t="n">
         <v>-225.17724616</v>
@@ -5646,7 +5646,7 @@
         <v>-224.60616436</v>
       </c>
       <c r="H163" t="n">
-        <v>-225.1754242419733</v>
+        <v>-225.1781170010103</v>
       </c>
     </row>
     <row r="164">
@@ -5669,7 +5669,7 @@
         <v>-0.6002294295903634</v>
       </c>
       <c r="E164" t="n">
-        <v>-0.5925564765930176</v>
+        <v>-0.5946063995361328</v>
       </c>
       <c r="F164" t="n">
         <v>-225.14977208</v>
@@ -5678,7 +5678,7 @@
         <v>-224.5495417</v>
       </c>
       <c r="H164" t="n">
-        <v>-225.142098176593</v>
+        <v>-225.1441480995361</v>
       </c>
     </row>
     <row r="165">
@@ -5701,7 +5701,7 @@
         <v>-0.5704414495511128</v>
       </c>
       <c r="E165" t="n">
-        <v>-0.5683345794677734</v>
+        <v>-0.5684452056884766</v>
       </c>
       <c r="F165" t="n">
         <v>-225.21035435</v>
@@ -5710,7 +5710,7 @@
         <v>-224.63991196</v>
       </c>
       <c r="H165" t="n">
-        <v>-225.2082465394678</v>
+        <v>-225.2083571656885</v>
       </c>
     </row>
     <row r="166">
@@ -5733,7 +5733,7 @@
         <v>-0.5733524371954738</v>
       </c>
       <c r="E166" t="n">
-        <v>-0.5736536383628845</v>
+        <v>-0.5716463327407837</v>
       </c>
       <c r="F166" t="n">
         <v>-225.22125643</v>
@@ -5742,7 +5742,7 @@
         <v>-224.64790343</v>
       </c>
       <c r="H166" t="n">
-        <v>-225.2215570683629</v>
+        <v>-225.2195497627408</v>
       </c>
     </row>
     <row r="167">
@@ -5765,7 +5765,7 @@
         <v>-0.5711219737240436</v>
       </c>
       <c r="E167" t="n">
-        <v>-0.5683357119560242</v>
+        <v>-0.5698710680007935</v>
       </c>
       <c r="F167" t="n">
         <v>-225.17651928</v>
@@ -5774,7 +5774,7 @@
         <v>-224.60539453</v>
       </c>
       <c r="H167" t="n">
-        <v>-225.173730241956</v>
+        <v>-225.1752655980008</v>
       </c>
     </row>
     <row r="168">
@@ -5797,7 +5797,7 @@
         <v>-0.6108802096492747</v>
       </c>
       <c r="E168" t="n">
-        <v>-0.6108037233352661</v>
+        <v>-0.6125486493110657</v>
       </c>
       <c r="F168" t="n">
         <v>-225.15434375</v>
@@ -5806,7 +5806,7 @@
         <v>-224.54346347</v>
       </c>
       <c r="H168" t="n">
-        <v>-225.1542671933353</v>
+        <v>-225.1560121193111</v>
       </c>
     </row>
     <row r="169">
@@ -5829,7 +5829,7 @@
         <v>-0.5749910171756087</v>
       </c>
       <c r="E169" t="n">
-        <v>-0.575688362121582</v>
+        <v>-0.5747301578521729</v>
       </c>
       <c r="F169" t="n">
         <v>-225.22428121</v>
@@ -5838,7 +5838,7 @@
         <v>-224.64929259</v>
       </c>
       <c r="H169" t="n">
-        <v>-225.2249809521216</v>
+        <v>-225.2240227478522</v>
       </c>
     </row>
     <row r="170">
@@ -5861,7 +5861,7 @@
         <v>-0.5702540858771374</v>
       </c>
       <c r="E170" t="n">
-        <v>-0.5683209896087646</v>
+        <v>-0.5663113594055176</v>
       </c>
       <c r="F170" t="n">
         <v>-225.20940896</v>
@@ -5870,7 +5870,7 @@
         <v>-224.63915726</v>
       </c>
       <c r="H170" t="n">
-        <v>-225.2074782496088</v>
+        <v>-225.2054686194055</v>
       </c>
     </row>
     <row r="171">
@@ -5893,7 +5893,7 @@
         <v>-0.5704027352646671</v>
       </c>
       <c r="E171" t="n">
-        <v>-0.5711432695388794</v>
+        <v>-0.5701923966407776</v>
       </c>
       <c r="F171" t="n">
         <v>-225.18983597</v>
@@ -5902,7 +5902,7 @@
         <v>-224.61943262</v>
       </c>
       <c r="H171" t="n">
-        <v>-225.1905758895389</v>
+        <v>-225.1896250166408</v>
       </c>
     </row>
     <row r="172">
@@ -5925,7 +5925,7 @@
         <v>-0.5701248721585801</v>
       </c>
       <c r="E172" t="n">
-        <v>-0.5709108114242554</v>
+        <v>-0.5700545310974121</v>
       </c>
       <c r="F172" t="n">
         <v>-225.19575344</v>
@@ -5934,7 +5934,7 @@
         <v>-224.62562713</v>
       </c>
       <c r="H172" t="n">
-        <v>-225.1965379414243</v>
+        <v>-225.1956816610974</v>
       </c>
     </row>
     <row r="173">
@@ -5957,7 +5957,7 @@
         <v>-0.5699653385809339</v>
       </c>
       <c r="E173" t="n">
-        <v>-0.5735102891921997</v>
+        <v>-0.5740475654602051</v>
       </c>
       <c r="F173" t="n">
         <v>-225.19954717</v>
@@ -5966,7 +5966,7 @@
         <v>-224.62958433</v>
       </c>
       <c r="H173" t="n">
-        <v>-225.2030946191922</v>
+        <v>-225.2036318954602</v>
       </c>
     </row>
     <row r="174">
@@ -5989,7 +5989,7 @@
         <v>-0.5709581541357873</v>
       </c>
       <c r="E174" t="n">
-        <v>-0.5697535872459412</v>
+        <v>-0.5689835548400879</v>
       </c>
       <c r="F174" t="n">
         <v>-225.17940998</v>
@@ -5998,7 +5998,7 @@
         <v>-224.60845364</v>
       </c>
       <c r="H174" t="n">
-        <v>-225.1782072272459</v>
+        <v>-225.1774371948401</v>
       </c>
     </row>
     <row r="175">
@@ -6021,7 +6021,7 @@
         <v>-0.6192689904278925</v>
       </c>
       <c r="E175" t="n">
-        <v>-0.614983081817627</v>
+        <v>-0.6187154650688171</v>
       </c>
       <c r="F175" t="n">
         <v>-225.15743269</v>
@@ -6030,7 +6030,7 @@
         <v>-224.53816308</v>
       </c>
       <c r="H175" t="n">
-        <v>-225.1531461618176</v>
+        <v>-225.1568785450688</v>
       </c>
     </row>
     <row r="176">
@@ -6053,7 +6053,7 @@
         <v>-0.6013007659520548</v>
       </c>
       <c r="E176" t="n">
-        <v>-0.5981501340866089</v>
+        <v>-0.6001764535903931</v>
       </c>
       <c r="F176" t="n">
         <v>-225.15021817</v>
@@ -6062,7 +6062,7 @@
         <v>-224.5489168</v>
       </c>
       <c r="H176" t="n">
-        <v>-225.1470669340866</v>
+        <v>-225.1490932535904</v>
       </c>
     </row>
     <row r="177">
@@ -6085,7 +6085,7 @@
         <v>-0.5729096553727843</v>
       </c>
       <c r="E177" t="n">
-        <v>-0.5755219459533691</v>
+        <v>-0.5729367733001709</v>
       </c>
       <c r="F177" t="n">
         <v>-225.15118321</v>
@@ -6094,7 +6094,7 @@
         <v>-224.5782734</v>
       </c>
       <c r="H177" t="n">
-        <v>-225.1537953459534</v>
+        <v>-225.1512101733002</v>
       </c>
     </row>
     <row r="178">
@@ -6117,7 +6117,7 @@
         <v>-0.5731118857062485</v>
       </c>
       <c r="E178" t="n">
-        <v>-0.5764105319976807</v>
+        <v>-0.572587251663208</v>
       </c>
       <c r="F178" t="n">
         <v>-225.14877168</v>
@@ -6126,7 +6126,7 @@
         <v>-224.57565879</v>
       </c>
       <c r="H178" t="n">
-        <v>-225.1520693219977</v>
+        <v>-225.1482460416632</v>
       </c>
     </row>
     <row r="179">
@@ -6149,7 +6149,7 @@
         <v>-0.5731797435136282</v>
       </c>
       <c r="E179" t="n">
-        <v>-0.5747948288917542</v>
+        <v>-0.5729889869689941</v>
       </c>
       <c r="F179" t="n">
         <v>-225.14796466</v>
@@ -6158,7 +6158,7 @@
         <v>-224.57478236</v>
       </c>
       <c r="H179" t="n">
-        <v>-225.1495771888918</v>
+        <v>-225.147771346969</v>
       </c>
     </row>
     <row r="180">
@@ -6181,7 +6181,7 @@
         <v>-0.5703375878757837</v>
       </c>
       <c r="E180" t="n">
-        <v>-0.5704604983329773</v>
+        <v>-0.5714761018753052</v>
       </c>
       <c r="F180" t="n">
         <v>-225.19117363</v>
@@ -6190,7 +6190,7 @@
         <v>-224.62083522</v>
       </c>
       <c r="H180" t="n">
-        <v>-225.191295718333</v>
+        <v>-225.1923113218753</v>
       </c>
     </row>
     <row r="181">
@@ -6213,7 +6213,7 @@
         <v>-0.5751519840580216</v>
       </c>
       <c r="E181" t="n">
-        <v>-0.577120840549469</v>
+        <v>-0.5787444114685059</v>
       </c>
       <c r="F181" t="n">
         <v>-225.12827565</v>
@@ -6222,7 +6222,7 @@
         <v>-224.55312442</v>
       </c>
       <c r="H181" t="n">
-        <v>-225.1302452605495</v>
+        <v>-225.1318688314685</v>
       </c>
     </row>
     <row r="182">
@@ -6245,7 +6245,7 @@
         <v>-0.5721145728579383</v>
       </c>
       <c r="E182" t="n">
-        <v>-0.5680767297744751</v>
+        <v>-0.5693688988685608</v>
       </c>
       <c r="F182" t="n">
         <v>-225.16144883</v>
@@ -6254,7 +6254,7 @@
         <v>-224.58933419</v>
       </c>
       <c r="H182" t="n">
-        <v>-225.1574109197745</v>
+        <v>-225.1587030888685</v>
       </c>
     </row>
     <row r="183">
@@ -6277,7 +6277,7 @@
         <v>-0.6055422136351515</v>
       </c>
       <c r="E183" t="n">
-        <v>-0.6030411124229431</v>
+        <v>-0.6050811409950256</v>
       </c>
       <c r="F183" t="n">
         <v>-225.15201382</v>
@@ -6286,7 +6286,7 @@
         <v>-224.54647198</v>
       </c>
       <c r="H183" t="n">
-        <v>-225.1495130924229</v>
+        <v>-225.151553120995</v>
       </c>
     </row>
     <row r="184">
@@ -6309,7 +6309,7 @@
         <v>-0.5697711150230107</v>
       </c>
       <c r="E184" t="n">
-        <v>-0.5695183277130127</v>
+        <v>-0.5722159147262573</v>
       </c>
       <c r="F184" t="n">
         <v>-225.20440807</v>
@@ -6318,7 +6318,7 @@
         <v>-224.63463806</v>
       </c>
       <c r="H184" t="n">
-        <v>-225.204156387713</v>
+        <v>-225.2068539747262</v>
       </c>
     </row>
     <row r="185">
@@ -6341,7 +6341,7 @@
         <v>-0.6160368873665898</v>
       </c>
       <c r="E185" t="n">
-        <v>-0.6167863607406616</v>
+        <v>-0.6202252507209778</v>
       </c>
       <c r="F185" t="n">
         <v>-225.15638976</v>
@@ -6350,7 +6350,7 @@
         <v>-224.54035778</v>
       </c>
       <c r="H185" t="n">
-        <v>-225.1571441407407</v>
+        <v>-225.160583030721</v>
       </c>
     </row>
     <row r="186">
@@ -6373,7 +6373,7 @@
         <v>-0.6098442393686759</v>
       </c>
       <c r="E186" t="n">
-        <v>-0.6083834767341614</v>
+        <v>-0.6085842847824097</v>
       </c>
       <c r="F186" t="n">
         <v>-225.15389276</v>
@@ -6382,7 +6382,7 @@
         <v>-224.54404918</v>
       </c>
       <c r="H186" t="n">
-        <v>-225.1524326567342</v>
+        <v>-225.1526334647824</v>
       </c>
     </row>
     <row r="187">
@@ -6405,7 +6405,7 @@
         <v>-0.5704371087797231</v>
       </c>
       <c r="E187" t="n">
-        <v>-0.569694995880127</v>
+        <v>-0.5683515667915344</v>
       </c>
       <c r="F187" t="n">
         <v>-225.18916231</v>
@@ -6414,7 +6414,7 @@
         <v>-224.61872573</v>
       </c>
       <c r="H187" t="n">
-        <v>-225.1884207258801</v>
+        <v>-225.1870772967915</v>
       </c>
     </row>
     <row r="188">
@@ -6437,7 +6437,7 @@
         <v>-0.572587066171758</v>
       </c>
       <c r="E188" t="n">
-        <v>-0.5724464058876038</v>
+        <v>-0.5720233917236328</v>
       </c>
       <c r="F188" t="n">
         <v>-225.15516913</v>
@@ -6446,7 +6446,7 @@
         <v>-224.58258094</v>
       </c>
       <c r="H188" t="n">
-        <v>-225.1550273458876</v>
+        <v>-225.1546043317236</v>
       </c>
     </row>
     <row r="189">
@@ -6469,7 +6469,7 @@
         <v>-0.5709141561186757</v>
       </c>
       <c r="E189" t="n">
-        <v>-0.5696657299995422</v>
+        <v>-0.5696355104446411</v>
       </c>
       <c r="F189" t="n">
         <v>-225.21257828</v>
@@ -6478,7 +6478,7 @@
         <v>-224.64166217</v>
       </c>
       <c r="H189" t="n">
-        <v>-225.2113278999995</v>
+        <v>-225.2112976804446</v>
       </c>
     </row>
     <row r="190">
@@ -6501,7 +6501,7 @@
         <v>-0.5750568988056839</v>
       </c>
       <c r="E190" t="n">
-        <v>-0.5741534233093262</v>
+        <v>-0.5776054859161377</v>
       </c>
       <c r="F190" t="n">
         <v>-225.12910319</v>
@@ -6510,7 +6510,7 @@
         <v>-224.55404706</v>
       </c>
       <c r="H190" t="n">
-        <v>-225.1282004833093</v>
+        <v>-225.1316525459161</v>
       </c>
     </row>
     <row r="191">
@@ -6533,7 +6533,7 @@
         <v>-0.6041273032535992</v>
       </c>
       <c r="E191" t="n">
-        <v>-0.6034951210021973</v>
+        <v>-0.6043243408203125</v>
       </c>
       <c r="F191" t="n">
         <v>-225.15140703</v>
@@ -6542,7 +6542,7 @@
         <v>-224.54728165</v>
       </c>
       <c r="H191" t="n">
-        <v>-225.1507767710022</v>
+        <v>-225.1516059908203</v>
       </c>
     </row>
     <row r="192">
@@ -6565,7 +6565,7 @@
         <v>-0.6102562577416173</v>
       </c>
       <c r="E192" t="n">
-        <v>-0.6104942560195923</v>
+        <v>-0.6090470552444458</v>
       </c>
       <c r="F192" t="n">
         <v>-225.15407087</v>
@@ -6574,7 +6574,7 @@
         <v>-224.54381946</v>
       </c>
       <c r="H192" t="n">
-        <v>-225.1543137160196</v>
+        <v>-225.1528665152445</v>
       </c>
     </row>
     <row r="193">
@@ -6597,7 +6597,7 @@
         <v>-0.5714417508472578</v>
       </c>
       <c r="E193" t="n">
-        <v>-0.5703972578048706</v>
+        <v>-0.5716781616210938</v>
       </c>
       <c r="F193" t="n">
         <v>-225.17135702</v>
@@ -6606,7 +6606,7 @@
         <v>-224.59991502</v>
       </c>
       <c r="H193" t="n">
-        <v>-225.1703122778049</v>
+        <v>-225.1715931816211</v>
       </c>
     </row>
     <row r="194">
@@ -6629,7 +6629,7 @@
         <v>-0.6187609460167294</v>
       </c>
       <c r="E194" t="n">
-        <v>-0.6174174547195435</v>
+        <v>-0.6174172759056091</v>
       </c>
       <c r="F194" t="n">
         <v>-225.15728178</v>
@@ -6638,7 +6638,7 @@
         <v>-224.53851726</v>
       </c>
       <c r="H194" t="n">
-        <v>-225.1559347147195</v>
+        <v>-225.1559345359056</v>
       </c>
     </row>
     <row r="195">
@@ -6661,7 +6661,7 @@
         <v>-0.5739274748551342</v>
       </c>
       <c r="E195" t="n">
-        <v>-0.5787173509597778</v>
+        <v>-0.5764079093933105</v>
       </c>
       <c r="F195" t="n">
         <v>-225.13982306</v>
@@ -6670,7 +6670,7 @@
         <v>-224.56589467</v>
       </c>
       <c r="H195" t="n">
-        <v>-225.1446120209598</v>
+        <v>-225.1423025793933</v>
       </c>
     </row>
     <row r="196">
@@ -6693,7 +6693,7 @@
         <v>-0.5716860285107872</v>
       </c>
       <c r="E196" t="n">
-        <v>-0.5711978673934937</v>
+        <v>-0.5715551376342773</v>
       </c>
       <c r="F196" t="n">
         <v>-225.16759332</v>
@@ -6702,7 +6702,7 @@
         <v>-224.59590604</v>
       </c>
       <c r="H196" t="n">
-        <v>-225.1671039073935</v>
+        <v>-225.1674611776343</v>
       </c>
     </row>
     <row r="197">
@@ -6725,7 +6725,7 @@
         <v>-0.5708361748825739</v>
       </c>
       <c r="E197" t="n">
-        <v>-0.5670732259750366</v>
+        <v>-0.5663728713989258</v>
       </c>
       <c r="F197" t="n">
         <v>-225.18154853</v>
@@ -6734,7 +6734,7 @@
         <v>-224.61071244</v>
       </c>
       <c r="H197" t="n">
-        <v>-225.177785665975</v>
+        <v>-225.1770853113989</v>
       </c>
     </row>
     <row r="198">
@@ -6757,7 +6757,7 @@
         <v>-0.6110895930740259</v>
       </c>
       <c r="E198" t="n">
-        <v>-0.6119070053100586</v>
+        <v>-0.6115751266479492</v>
       </c>
       <c r="F198" t="n">
         <v>-225.15443649</v>
@@ -6766,7 +6766,7 @@
         <v>-224.54334155</v>
       </c>
       <c r="H198" t="n">
-        <v>-225.1552485553101</v>
+        <v>-225.154916676648</v>
       </c>
     </row>
     <row r="199">
@@ -6789,7 +6789,7 @@
         <v>-0.5738734471869026</v>
       </c>
       <c r="E199" t="n">
-        <v>-0.5775442123413086</v>
+        <v>-0.575197696685791</v>
       </c>
       <c r="F199" t="n">
         <v>-225.22246863</v>
@@ -6798,7 +6798,7 @@
         <v>-224.64859473</v>
       </c>
       <c r="H199" t="n">
-        <v>-225.2261389423413</v>
+        <v>-225.2237924266858</v>
       </c>
     </row>
     <row r="200">
@@ -6821,7 +6821,7 @@
         <v>-0.569939506300287</v>
       </c>
       <c r="E200" t="n">
-        <v>-0.5730068683624268</v>
+        <v>-0.5741118788719177</v>
       </c>
       <c r="F200" t="n">
         <v>-225.20016739</v>
@@ -6830,7 +6830,7 @@
         <v>-224.63023023</v>
       </c>
       <c r="H200" t="n">
-        <v>-225.2032370983624</v>
+        <v>-225.2043421088719</v>
       </c>
     </row>
     <row r="201">
@@ -6853,7 +6853,7 @@
         <v>-0.6050084952480437</v>
       </c>
       <c r="E201" t="n">
-        <v>-0.6047862768173218</v>
+        <v>-0.6047990918159485</v>
       </c>
       <c r="F201" t="n">
         <v>-225.15178476</v>
@@ -6862,7 +6862,7 @@
         <v>-224.5467757</v>
       </c>
       <c r="H201" t="n">
-        <v>-225.1515619768173</v>
+        <v>-225.151574791816</v>
       </c>
     </row>
     <row r="202">
@@ -6885,7 +6885,7 @@
         <v>-0.5697670201357057</v>
       </c>
       <c r="E202" t="n">
-        <v>-0.5768206119537354</v>
+        <v>-0.5725964307785034</v>
       </c>
       <c r="F202" t="n">
         <v>-225.20690307</v>
@@ -6894,7 +6894,7 @@
         <v>-224.63713408</v>
       </c>
       <c r="H202" t="n">
-        <v>-225.2139546919537</v>
+        <v>-225.2097305107785</v>
       </c>
     </row>
     <row r="203">
@@ -6917,7 +6917,7 @@
         <v>-0.5724685057406937</v>
       </c>
       <c r="E203" t="n">
-        <v>-0.572798490524292</v>
+        <v>-0.5721185803413391</v>
       </c>
       <c r="F203" t="n">
         <v>-225.2186757</v>
@@ -6926,7 +6926,7 @@
         <v>-224.64620483</v>
       </c>
       <c r="H203" t="n">
-        <v>-225.2190033205243</v>
+        <v>-225.2183234103413</v>
       </c>
     </row>
     <row r="204">
@@ -6949,7 +6949,7 @@
         <v>-0.5694504072074273</v>
       </c>
       <c r="E204" t="n">
-        <v>-0.570536732673645</v>
+        <v>-0.5695686340332031</v>
       </c>
       <c r="F204" t="n">
         <v>-225.21393834</v>
@@ -6958,7 +6958,7 @@
         <v>-224.64448761</v>
       </c>
       <c r="H204" t="n">
-        <v>-225.2150243426736</v>
+        <v>-225.2140562440332</v>
       </c>
     </row>
     <row r="205">
@@ -6981,7 +6981,7 @@
         <v>-0.5696707224692732</v>
       </c>
       <c r="E205" t="n">
-        <v>-0.5747065544128418</v>
+        <v>-0.5701491832733154</v>
       </c>
       <c r="F205" t="n">
         <v>-225.20637742</v>
@@ -6990,7 +6990,7 @@
         <v>-224.63670634</v>
       </c>
       <c r="H205" t="n">
-        <v>-225.2114128944128</v>
+        <v>-225.2068555232733</v>
       </c>
     </row>
     <row r="206">
@@ -7013,7 +7013,7 @@
         <v>-0.5694819473119066</v>
       </c>
       <c r="E206" t="n">
-        <v>-0.5704050064086914</v>
+        <v>-0.5694417953491211</v>
       </c>
       <c r="F206" t="n">
         <v>-225.21287624</v>
@@ -7022,7 +7022,7 @@
         <v>-224.64339413</v>
       </c>
       <c r="H206" t="n">
-        <v>-225.2137991364087</v>
+        <v>-225.2128359253491</v>
       </c>
     </row>
     <row r="207">
@@ -7045,7 +7045,7 @@
         <v>-0.5734696190076687</v>
       </c>
       <c r="E207" t="n">
-        <v>-0.5771687030792236</v>
+        <v>-0.5760291814804077</v>
       </c>
       <c r="F207" t="n">
         <v>-225.14472311</v>
@@ -7054,7 +7054,7 @@
         <v>-224.57125388</v>
       </c>
       <c r="H207" t="n">
-        <v>-225.1484225830792</v>
+        <v>-225.1472830614804</v>
       </c>
     </row>
     <row r="208">
@@ -7077,7 +7077,7 @@
         <v>-0.5713958008330706</v>
       </c>
       <c r="E208" t="n">
-        <v>-0.570745050907135</v>
+        <v>-0.5721142292022705</v>
       </c>
       <c r="F208" t="n">
         <v>-225.17210243</v>
@@ -7086,7 +7086,7 @@
         <v>-224.6007076</v>
       </c>
       <c r="H208" t="n">
-        <v>-225.1714526509071</v>
+        <v>-225.1728218292023</v>
       </c>
     </row>
     <row r="209">
@@ -7109,7 +7109,7 @@
         <v>-0.5980477072446154</v>
       </c>
       <c r="E209" t="n">
-        <v>-0.5995821952819824</v>
+        <v>-0.5986230373382568</v>
       </c>
       <c r="F209" t="n">
         <v>-225.14886826</v>
@@ -7118,7 +7118,7 @@
         <v>-224.55081876</v>
       </c>
       <c r="H209" t="n">
-        <v>-225.150400955282</v>
+        <v>-225.1494417973383</v>
       </c>
     </row>
     <row r="210">
@@ -7141,7 +7141,7 @@
         <v>-0.6084749786581357</v>
       </c>
       <c r="E210" t="n">
-        <v>-0.607577383518219</v>
+        <v>-0.6071217060089111</v>
       </c>
       <c r="F210" t="n">
         <v>-225.1532912</v>
@@ -7150,7 +7150,7 @@
         <v>-224.54481821</v>
       </c>
       <c r="H210" t="n">
-        <v>-225.1523955935182</v>
+        <v>-225.1519399160089</v>
       </c>
     </row>
     <row r="211">
@@ -7173,7 +7173,7 @@
         <v>-0.5713487626901996</v>
       </c>
       <c r="E211" t="n">
-        <v>-0.5705530643463135</v>
+        <v>-0.5726224184036255</v>
       </c>
       <c r="F211" t="n">
         <v>-225.17284518</v>
@@ -7182,7 +7182,7 @@
         <v>-224.60149696</v>
       </c>
       <c r="H211" t="n">
-        <v>-225.1720500243463</v>
+        <v>-225.1741193784036</v>
       </c>
     </row>
     <row r="212">
@@ -7205,7 +7205,7 @@
         <v>-0.5745611443759882</v>
       </c>
       <c r="E212" t="n">
-        <v>-0.5741372108459473</v>
+        <v>-0.5690937042236328</v>
       </c>
       <c r="F212" t="n">
         <v>-225.22371189</v>
@@ -7214,7 +7214,7 @@
         <v>-224.64915037</v>
       </c>
       <c r="H212" t="n">
-        <v>-225.2232875808459</v>
+        <v>-225.2182440742236</v>
       </c>
     </row>
     <row r="213">
@@ -7237,7 +7237,7 @@
         <v>-0.569353394418747</v>
       </c>
       <c r="E213" t="n">
-        <v>-0.5687158703804016</v>
+        <v>-0.5671446323394775</v>
       </c>
       <c r="F213" t="n">
         <v>-225.2175253</v>
@@ -7246,7 +7246,7 @@
         <v>-224.64817153</v>
       </c>
       <c r="H213" t="n">
-        <v>-225.2168874003804</v>
+        <v>-225.2153161623395</v>
       </c>
     </row>
   </sheetData>
